--- a/sim_samples.xlsx
+++ b/sim_samples.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Grant\Desktop\Projects\capsim_model\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\grant\OneDrive\Desktop\repos\capsim_model\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{338280A2-05EC-4777-9225-2CBF48315127}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BEFF24C-9305-4DF5-B44A-781A57F56BD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="38430" windowHeight="21030" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="11520" windowHeight="12360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Raw" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="417" uniqueCount="34">
   <si>
     <t>Catagroie</t>
   </si>
@@ -134,6 +134,12 @@
   <si>
     <t>Awarness%</t>
   </si>
+  <si>
+    <t>H_R1</t>
+  </si>
+  <si>
+    <t>H_R2</t>
+  </si>
 </sst>
 </file>
 
@@ -187,7 +193,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="72">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
       <alignment shrinkToFit="1"/>
@@ -217,6 +223,189 @@
       <alignment shrinkToFit="1"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
+      <alignment shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment shrinkToFit="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -498,27 +687,27 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AB118"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:AB190"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" customWidth="1"/>
-    <col min="7" max="7" width="13.85546875" customWidth="1"/>
-    <col min="8" max="8" width="14.140625" customWidth="1"/>
-    <col min="9" max="9" width="11.42578125" customWidth="1"/>
-    <col min="12" max="12" width="11.140625" customWidth="1"/>
-    <col min="14" max="14" width="13.28515625" customWidth="1"/>
-    <col min="15" max="15" width="16.85546875" customWidth="1"/>
-    <col min="21" max="21" width="10.5703125" customWidth="1"/>
+    <col min="5" max="5" width="14.44140625" customWidth="1"/>
+    <col min="7" max="7" width="13.88671875" customWidth="1"/>
+    <col min="8" max="8" width="14.109375" customWidth="1"/>
+    <col min="9" max="9" width="11.44140625" customWidth="1"/>
+    <col min="12" max="12" width="11.109375" customWidth="1"/>
+    <col min="14" max="14" width="13.33203125" customWidth="1"/>
+    <col min="15" max="15" width="16.88671875" customWidth="1"/>
+    <col min="21" max="21" width="10.5546875" customWidth="1"/>
     <col min="22" max="22" width="11" customWidth="1"/>
-    <col min="23" max="23" width="10.5703125" customWidth="1"/>
-    <col min="24" max="24" width="14.42578125" customWidth="1"/>
-    <col min="25" max="25" width="9.42578125" customWidth="1"/>
-    <col min="26" max="26" width="12.7109375" customWidth="1"/>
-    <col min="27" max="27" width="13.42578125" customWidth="1"/>
+    <col min="23" max="23" width="10.5546875" customWidth="1"/>
+    <col min="24" max="24" width="14.44140625" customWidth="1"/>
+    <col min="25" max="25" width="9.44140625" customWidth="1"/>
+    <col min="26" max="26" width="12.6640625" customWidth="1"/>
+    <col min="27" max="27" width="13.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -597,7 +786,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="2" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -680,7 +869,7 @@
         <v>0.64599999999999991</v>
       </c>
     </row>
-    <row r="3" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -763,7 +952,7 @@
         <v>0.81700000000000006</v>
       </c>
     </row>
-    <row r="4" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -846,7 +1035,7 @@
         <v>0.58299999999999996</v>
       </c>
     </row>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -929,7 +1118,7 @@
         <v>0.58299999999999996</v>
       </c>
     </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -1012,7 +1201,7 @@
         <v>0.58299999999999996</v>
       </c>
     </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>4</v>
       </c>
@@ -1089,7 +1278,7 @@
         <v>0.55000000000000004</v>
       </c>
     </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>18</v>
       </c>
@@ -1166,7 +1355,7 @@
         <v>0.624</v>
       </c>
     </row>
-    <row r="9" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>18</v>
       </c>
@@ -1243,7 +1432,7 @@
         <v>0.52900000000000003</v>
       </c>
     </row>
-    <row r="10" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>18</v>
       </c>
@@ -1320,7 +1509,7 @@
         <v>0.79599999999999993</v>
       </c>
     </row>
-    <row r="11" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>18</v>
       </c>
@@ -1397,7 +1586,7 @@
         <v>0.52900000000000003</v>
       </c>
     </row>
-    <row r="12" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>18</v>
       </c>
@@ -1474,7 +1663,7 @@
         <v>0.52900000000000003</v>
       </c>
     </row>
-    <row r="13" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>18</v>
       </c>
@@ -1551,7 +1740,7 @@
         <v>0.51700000000000002</v>
       </c>
     </row>
-    <row r="14" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>19</v>
       </c>
@@ -1628,7 +1817,7 @@
         <v>0.77400000000000002</v>
       </c>
     </row>
-    <row r="15" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>19</v>
       </c>
@@ -1705,7 +1894,7 @@
         <v>0.60299999999999998</v>
       </c>
     </row>
-    <row r="16" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>19</v>
       </c>
@@ -1782,7 +1971,7 @@
         <v>0.47600000000000003</v>
       </c>
     </row>
-    <row r="17" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>19</v>
       </c>
@@ -1859,7 +2048,7 @@
         <v>0.47600000000000003</v>
       </c>
     </row>
-    <row r="18" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>19</v>
       </c>
@@ -1936,7 +2125,7 @@
         <v>0.47600000000000003</v>
       </c>
     </row>
-    <row r="19" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>19</v>
       </c>
@@ -2013,7 +2202,7 @@
         <v>0.48599999999999999</v>
       </c>
     </row>
-    <row r="20" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>6</v>
       </c>
@@ -2090,7 +2279,7 @@
         <v>0.754</v>
       </c>
     </row>
-    <row r="21" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>6</v>
       </c>
@@ -2167,7 +2356,7 @@
         <v>0.58200000000000007</v>
       </c>
     </row>
-    <row r="22" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>6</v>
       </c>
@@ -2244,7 +2433,7 @@
         <v>0.42499999999999999</v>
       </c>
     </row>
-    <row r="23" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>6</v>
       </c>
@@ -2321,7 +2510,7 @@
         <v>0.42499999999999999</v>
       </c>
     </row>
-    <row r="24" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>6</v>
       </c>
@@ -2398,7 +2587,7 @@
         <v>0.42499999999999999</v>
       </c>
     </row>
-    <row r="25" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>6</v>
       </c>
@@ -2475,7 +2664,7 @@
         <v>0.45500000000000002</v>
       </c>
     </row>
-    <row r="26" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>7</v>
       </c>
@@ -2552,7 +2741,7 @@
         <v>0.754</v>
       </c>
     </row>
-    <row r="27" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>7</v>
       </c>
@@ -2629,7 +2818,7 @@
         <v>0.42499999999999999</v>
       </c>
     </row>
-    <row r="28" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>7</v>
       </c>
@@ -2706,7 +2895,7 @@
         <v>0.503</v>
       </c>
     </row>
-    <row r="29" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>7</v>
       </c>
@@ -2783,7 +2972,7 @@
         <v>0.42499999999999999</v>
       </c>
     </row>
-    <row r="30" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>7</v>
       </c>
@@ -2860,7 +3049,7 @@
         <v>0.42499999999999999</v>
       </c>
     </row>
-    <row r="31" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>7</v>
       </c>
@@ -2937,7 +3126,7 @@
         <v>0.45500000000000002</v>
       </c>
     </row>
-    <row r="32" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>4</v>
       </c>
@@ -3014,7 +3203,7 @@
         <v>0.67500000000000004</v>
       </c>
     </row>
-    <row r="33" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>4</v>
       </c>
@@ -3091,7 +3280,7 @@
         <v>0.55100000000000005</v>
       </c>
     </row>
-    <row r="34" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>4</v>
       </c>
@@ -3168,7 +3357,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="35" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>4</v>
       </c>
@@ -3245,7 +3434,7 @@
         <v>0.81700000000000006</v>
       </c>
     </row>
-    <row r="36" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>4</v>
       </c>
@@ -3322,7 +3511,7 @@
         <v>0.58299999999999996</v>
       </c>
     </row>
-    <row r="37" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>4</v>
       </c>
@@ -3399,7 +3588,7 @@
         <v>0.79599999999999993</v>
       </c>
     </row>
-    <row r="38" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>4</v>
       </c>
@@ -3476,7 +3665,7 @@
         <v>0.52900000000000003</v>
       </c>
     </row>
-    <row r="39" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>4</v>
       </c>
@@ -3553,7 +3742,7 @@
         <v>0.624</v>
       </c>
     </row>
-    <row r="40" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>4</v>
       </c>
@@ -3630,7 +3819,7 @@
         <v>0.70599999999999996</v>
       </c>
     </row>
-    <row r="41" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>4</v>
       </c>
@@ -3707,7 +3896,7 @@
         <v>0.52900000000000003</v>
       </c>
     </row>
-    <row r="42" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>4</v>
       </c>
@@ -3784,7 +3973,7 @@
         <v>0.42499999999999999</v>
       </c>
     </row>
-    <row r="43" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>4</v>
       </c>
@@ -3861,7 +4050,7 @@
         <v>0.754</v>
       </c>
     </row>
-    <row r="44" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>18</v>
       </c>
@@ -3938,7 +4127,7 @@
         <v>0.52900000000000003</v>
       </c>
     </row>
-    <row r="45" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>18</v>
       </c>
@@ -4015,7 +4204,7 @@
         <v>0.624</v>
       </c>
     </row>
-    <row r="46" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>18</v>
       </c>
@@ -4092,7 +4281,7 @@
         <v>0.79599999999999993</v>
       </c>
     </row>
-    <row r="47" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>18</v>
       </c>
@@ -4169,7 +4358,7 @@
         <v>0.52900000000000003</v>
       </c>
     </row>
-    <row r="48" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>18</v>
       </c>
@@ -4246,7 +4435,7 @@
         <v>0.70599999999999996</v>
       </c>
     </row>
-    <row r="49" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>18</v>
       </c>
@@ -4323,7 +4512,7 @@
         <v>0.58299999999999996</v>
       </c>
     </row>
-    <row r="50" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>18</v>
       </c>
@@ -4400,7 +4589,7 @@
         <v>0.55100000000000005</v>
       </c>
     </row>
-    <row r="51" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>18</v>
       </c>
@@ -4477,7 +4666,7 @@
         <v>0.81700000000000006</v>
       </c>
     </row>
-    <row r="52" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>19</v>
       </c>
@@ -4554,7 +4743,7 @@
         <v>0.77400000000000002</v>
       </c>
     </row>
-    <row r="53" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>19</v>
       </c>
@@ -4631,7 +4820,7 @@
         <v>0.63200000000000001</v>
       </c>
     </row>
-    <row r="54" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>19</v>
       </c>
@@ -4708,7 +4897,7 @@
         <v>0.65900000000000003</v>
       </c>
     </row>
-    <row r="55" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>19</v>
       </c>
@@ -4785,7 +4974,7 @@
         <v>0.60299999999999998</v>
       </c>
     </row>
-    <row r="56" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>19</v>
       </c>
@@ -4862,7 +5051,7 @@
         <v>0.47600000000000003</v>
       </c>
     </row>
-    <row r="57" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>19</v>
       </c>
@@ -4939,7 +5128,7 @@
         <v>0.754</v>
       </c>
     </row>
-    <row r="58" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>19</v>
       </c>
@@ -5016,7 +5205,7 @@
         <v>0.77800000000000002</v>
       </c>
     </row>
-    <row r="59" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>19</v>
       </c>
@@ -5093,7 +5282,7 @@
         <v>0.42499999999999999</v>
       </c>
     </row>
-    <row r="60" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>19</v>
       </c>
@@ -5170,7 +5359,7 @@
         <v>0.58200000000000007</v>
       </c>
     </row>
-    <row r="61" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>19</v>
       </c>
@@ -5247,7 +5436,7 @@
         <v>0.81700000000000006</v>
       </c>
     </row>
-    <row r="62" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>19</v>
       </c>
@@ -5324,7 +5513,7 @@
         <v>0.55100000000000005</v>
       </c>
     </row>
-    <row r="63" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>19</v>
       </c>
@@ -5401,7 +5590,7 @@
         <v>0.55100000000000005</v>
       </c>
     </row>
-    <row r="64" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>6</v>
       </c>
@@ -5478,7 +5667,7 @@
         <v>0.77800000000000002</v>
       </c>
     </row>
-    <row r="65" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>6</v>
       </c>
@@ -5555,7 +5744,7 @@
         <v>0.754</v>
       </c>
     </row>
-    <row r="66" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>6</v>
       </c>
@@ -5632,7 +5821,7 @@
         <v>0.58200000000000007</v>
       </c>
     </row>
-    <row r="67" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>6</v>
       </c>
@@ -5709,7 +5898,7 @@
         <v>0.55100000000000005</v>
       </c>
     </row>
-    <row r="68" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>6</v>
       </c>
@@ -5786,7 +5975,7 @@
         <v>0.42499999999999999</v>
       </c>
     </row>
-    <row r="69" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>6</v>
       </c>
@@ -5863,7 +6052,7 @@
         <v>0.55100000000000005</v>
       </c>
     </row>
-    <row r="70" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>6</v>
       </c>
@@ -5940,7 +6129,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="71" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>6</v>
       </c>
@@ -6017,7 +6206,7 @@
         <v>0.81700000000000006</v>
       </c>
     </row>
-    <row r="72" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>7</v>
       </c>
@@ -6094,7 +6283,7 @@
         <v>0.754</v>
       </c>
     </row>
-    <row r="73" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>7</v>
       </c>
@@ -6171,7 +6360,7 @@
         <v>0.754</v>
       </c>
     </row>
-    <row r="74" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>7</v>
       </c>
@@ -6248,7 +6437,7 @@
         <v>0.55100000000000005</v>
       </c>
     </row>
-    <row r="75" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>7</v>
       </c>
@@ -6325,7 +6514,7 @@
         <v>0.42499999999999999</v>
       </c>
     </row>
-    <row r="76" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>7</v>
       </c>
@@ -6402,7 +6591,7 @@
         <v>0.55100000000000005</v>
       </c>
     </row>
-    <row r="77" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>7</v>
       </c>
@@ -6479,7 +6668,7 @@
         <v>0.81700000000000006</v>
       </c>
     </row>
-    <row r="78" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>7</v>
       </c>
@@ -6556,7 +6745,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="79" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>7</v>
       </c>
@@ -6633,7 +6822,7 @@
         <v>0.67500000000000004</v>
       </c>
     </row>
-    <row r="80" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>7</v>
       </c>
@@ -6710,7 +6899,7 @@
         <v>0.58299999999999996</v>
       </c>
     </row>
-    <row r="81" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>4</v>
       </c>
@@ -6787,7 +6976,7 @@
         <v>0.88500000000000001</v>
       </c>
     </row>
-    <row r="82" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>4</v>
       </c>
@@ -6864,7 +7053,7 @@
         <v>0.75900000000000001</v>
       </c>
     </row>
-    <row r="83" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>4</v>
       </c>
@@ -6941,7 +7130,7 @@
         <v>0.996</v>
       </c>
     </row>
-    <row r="84" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>4</v>
       </c>
@@ -7018,7 +7207,7 @@
         <v>0.70299999999999996</v>
       </c>
     </row>
-    <row r="85" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>4</v>
       </c>
@@ -7095,7 +7284,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="86" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>4</v>
       </c>
@@ -7172,7 +7361,7 @@
         <v>0.98199999999999998</v>
       </c>
     </row>
-    <row r="87" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>18</v>
       </c>
@@ -7249,7 +7438,7 @@
         <v>0.752</v>
       </c>
     </row>
-    <row r="88" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>18</v>
       </c>
@@ -7326,7 +7515,7 @@
         <v>0.98199999999999998</v>
       </c>
     </row>
-    <row r="89" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>18</v>
       </c>
@@ -7403,7 +7592,7 @@
         <v>0.68900000000000006</v>
       </c>
     </row>
-    <row r="90" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>18</v>
       </c>
@@ -7480,7 +7669,7 @@
         <v>0.83200000000000007</v>
       </c>
     </row>
-    <row r="91" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>18</v>
       </c>
@@ -7557,7 +7746,7 @@
         <v>0.71400000000000008</v>
       </c>
     </row>
-    <row r="92" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>18</v>
       </c>
@@ -7634,7 +7823,7 @@
         <v>0.70299999999999996</v>
       </c>
     </row>
-    <row r="93" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>18</v>
       </c>
@@ -7711,7 +7900,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="94" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>18</v>
       </c>
@@ -7788,7 +7977,7 @@
         <v>0.88500000000000001</v>
       </c>
     </row>
-    <row r="95" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>18</v>
       </c>
@@ -7865,7 +8054,7 @@
         <v>0.75900000000000001</v>
       </c>
     </row>
-    <row r="96" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>19</v>
       </c>
@@ -7942,7 +8131,7 @@
         <v>0.878</v>
       </c>
     </row>
-    <row r="97" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>19</v>
       </c>
@@ -8019,7 +8208,7 @@
         <v>0.80599999999999994</v>
       </c>
     </row>
-    <row r="98" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>19</v>
       </c>
@@ -8096,7 +8285,7 @@
         <v>0.96799999999999997</v>
       </c>
     </row>
-    <row r="99" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>19</v>
       </c>
@@ -8173,7 +8362,7 @@
         <v>0.68099999999999994</v>
       </c>
     </row>
-    <row r="100" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>19</v>
       </c>
@@ -8250,7 +8439,7 @@
         <v>0.76800000000000002</v>
       </c>
     </row>
-    <row r="101" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>19</v>
       </c>
@@ -8327,7 +8516,7 @@
         <v>0.64400000000000002</v>
       </c>
     </row>
-    <row r="102" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>19</v>
       </c>
@@ -8404,7 +8593,7 @@
         <v>0.996</v>
       </c>
     </row>
-    <row r="103" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>19</v>
       </c>
@@ -8481,7 +8670,7 @@
         <v>0.88500000000000001</v>
       </c>
     </row>
-    <row r="104" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>19</v>
       </c>
@@ -8558,7 +8747,7 @@
         <v>0.75900000000000001</v>
       </c>
     </row>
-    <row r="105" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A105" s="4" t="s">
         <v>6</v>
       </c>
@@ -8635,7 +8824,7 @@
         <v>0.85499999999999998</v>
       </c>
     </row>
-    <row r="106" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A106" s="4" t="s">
         <v>6</v>
       </c>
@@ -8712,7 +8901,7 @@
         <v>0.74900000000000011</v>
       </c>
     </row>
-    <row r="107" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A107" s="4" t="s">
         <v>6</v>
       </c>
@@ -8789,7 +8978,7 @@
         <v>0.95400000000000007</v>
       </c>
     </row>
-    <row r="108" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A108" s="4" t="s">
         <v>6</v>
       </c>
@@ -8866,7 +9055,7 @@
         <v>0.61599999999999999</v>
       </c>
     </row>
-    <row r="109" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A109" s="4" t="s">
         <v>6</v>
       </c>
@@ -8943,7 +9132,7 @@
         <v>0.64400000000000002</v>
       </c>
     </row>
-    <row r="110" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>7</v>
       </c>
@@ -9020,7 +9209,7 @@
         <v>0.95400000000000007</v>
       </c>
     </row>
-    <row r="111" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>7</v>
       </c>
@@ -9097,7 +9286,7 @@
         <v>0.61599999999999999</v>
       </c>
     </row>
-    <row r="112" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>7</v>
       </c>
@@ -9174,7 +9363,7 @@
         <v>0.95400000000000007</v>
       </c>
     </row>
-    <row r="113" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>7</v>
       </c>
@@ -9251,7 +9440,7 @@
         <v>0.64400000000000002</v>
       </c>
     </row>
-    <row r="114" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>7</v>
       </c>
@@ -9328,7 +9517,7 @@
         <v>0.70299999999999996</v>
       </c>
     </row>
-    <row r="115" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>7</v>
       </c>
@@ -9405,7 +9594,7 @@
         <v>0.996</v>
       </c>
     </row>
-    <row r="116" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>7</v>
       </c>
@@ -9482,7 +9671,7 @@
         <v>0.88500000000000001</v>
       </c>
     </row>
-    <row r="117" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>7</v>
       </c>
@@ -9559,7 +9748,7 @@
         <v>0.75900000000000001</v>
       </c>
     </row>
-    <row r="118" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>7</v>
       </c>
@@ -9634,6 +9823,3606 @@
       </c>
       <c r="AB118" s="10">
         <v>0.75</v>
+      </c>
+    </row>
+    <row r="119" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A119" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="B119" s="13">
+        <v>27.75</v>
+      </c>
+      <c r="C119" s="14">
+        <v>24.5</v>
+      </c>
+      <c r="D119" s="16">
+        <v>1521</v>
+      </c>
+      <c r="E119" s="17">
+        <v>10756</v>
+      </c>
+      <c r="F119" s="18">
+        <v>2.4</v>
+      </c>
+      <c r="G119">
+        <v>2</v>
+      </c>
+      <c r="H119" s="19">
+        <v>5.7</v>
+      </c>
+      <c r="I119" s="15">
+        <v>5.7</v>
+      </c>
+      <c r="J119" s="21">
+        <v>14.3</v>
+      </c>
+      <c r="K119" s="15">
+        <v>14.3</v>
+      </c>
+      <c r="L119" s="22">
+        <v>18000</v>
+      </c>
+      <c r="M119" s="15">
+        <v>16500</v>
+      </c>
+      <c r="N119" s="23">
+        <v>0.65</v>
+      </c>
+      <c r="O119" s="24">
+        <v>0.81700000000000006</v>
+      </c>
+      <c r="P119" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="120" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A120" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="B120" s="13">
+        <v>27.5</v>
+      </c>
+      <c r="C120" s="14">
+        <v>24.5</v>
+      </c>
+      <c r="D120" s="16">
+        <v>1415</v>
+      </c>
+      <c r="E120" s="17">
+        <v>10756</v>
+      </c>
+      <c r="F120" s="18">
+        <v>2.4</v>
+      </c>
+      <c r="G120">
+        <v>2</v>
+      </c>
+      <c r="H120" s="19">
+        <v>5.7</v>
+      </c>
+      <c r="I120" s="15">
+        <v>5.7</v>
+      </c>
+      <c r="J120" s="21">
+        <v>14.3</v>
+      </c>
+      <c r="K120" s="15">
+        <v>14.3</v>
+      </c>
+      <c r="L120" s="22">
+        <v>17500</v>
+      </c>
+      <c r="M120" s="15">
+        <v>16500</v>
+      </c>
+      <c r="N120" s="23">
+        <v>0.65</v>
+      </c>
+      <c r="O120" s="24">
+        <v>0.75</v>
+      </c>
+      <c r="P120" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="121" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A121" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="B121" s="13">
+        <v>24.5</v>
+      </c>
+      <c r="C121" s="14">
+        <v>24.5</v>
+      </c>
+      <c r="D121" s="16">
+        <v>1390</v>
+      </c>
+      <c r="E121" s="17">
+        <v>10756</v>
+      </c>
+      <c r="F121" s="18">
+        <v>2.4</v>
+      </c>
+      <c r="G121">
+        <v>2</v>
+      </c>
+      <c r="H121" s="19">
+        <v>5.9</v>
+      </c>
+      <c r="I121" s="15">
+        <v>5.7</v>
+      </c>
+      <c r="J121" s="21">
+        <v>14.5</v>
+      </c>
+      <c r="K121" s="15">
+        <v>14.3</v>
+      </c>
+      <c r="L121" s="22">
+        <v>17500</v>
+      </c>
+      <c r="M121" s="15">
+        <v>16500</v>
+      </c>
+      <c r="N121" s="23">
+        <v>0.61</v>
+      </c>
+      <c r="O121" s="24">
+        <v>0.61499999999999999</v>
+      </c>
+      <c r="P121" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="122" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A122" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="B122" s="13">
+        <v>26.5</v>
+      </c>
+      <c r="C122" s="14">
+        <v>24.5</v>
+      </c>
+      <c r="D122" s="16">
+        <v>1245</v>
+      </c>
+      <c r="E122" s="17">
+        <v>10756</v>
+      </c>
+      <c r="F122" s="18">
+        <v>2.4</v>
+      </c>
+      <c r="G122">
+        <v>2</v>
+      </c>
+      <c r="H122" s="19">
+        <v>5.7</v>
+      </c>
+      <c r="I122" s="15">
+        <v>5.7</v>
+      </c>
+      <c r="J122" s="21">
+        <v>14.3</v>
+      </c>
+      <c r="K122" s="15">
+        <v>14.3</v>
+      </c>
+      <c r="L122" s="22">
+        <v>17500</v>
+      </c>
+      <c r="M122" s="15">
+        <v>16500</v>
+      </c>
+      <c r="N122" s="23">
+        <v>0.67</v>
+      </c>
+      <c r="O122" s="24">
+        <v>0.81700000000000006</v>
+      </c>
+      <c r="P122" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="123" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A123" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="B123" s="13">
+        <v>29.75</v>
+      </c>
+      <c r="C123" s="14">
+        <v>24.5</v>
+      </c>
+      <c r="D123" s="16">
+        <v>1126</v>
+      </c>
+      <c r="E123" s="17">
+        <v>10756</v>
+      </c>
+      <c r="F123" s="18">
+        <v>2.4</v>
+      </c>
+      <c r="G123">
+        <v>2</v>
+      </c>
+      <c r="H123" s="19">
+        <v>6</v>
+      </c>
+      <c r="I123" s="15">
+        <v>5.7</v>
+      </c>
+      <c r="J123" s="21">
+        <v>14.2</v>
+      </c>
+      <c r="K123" s="15">
+        <v>14.3</v>
+      </c>
+      <c r="L123" s="22">
+        <v>17000</v>
+      </c>
+      <c r="M123" s="15">
+        <v>16500</v>
+      </c>
+      <c r="N123" s="23">
+        <v>0.66</v>
+      </c>
+      <c r="O123" s="24">
+        <v>0.80400000000000005</v>
+      </c>
+      <c r="P123" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="124" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A124" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="B124" s="13">
+        <v>29</v>
+      </c>
+      <c r="C124" s="14">
+        <v>24.5</v>
+      </c>
+      <c r="D124" s="16">
+        <v>1124</v>
+      </c>
+      <c r="E124" s="17">
+        <v>10756</v>
+      </c>
+      <c r="F124" s="18">
+        <v>2.4</v>
+      </c>
+      <c r="G124">
+        <v>2</v>
+      </c>
+      <c r="H124" s="19">
+        <v>5.7</v>
+      </c>
+      <c r="I124" s="15">
+        <v>5.7</v>
+      </c>
+      <c r="J124" s="21">
+        <v>14.3</v>
+      </c>
+      <c r="K124" s="15">
+        <v>14.3</v>
+      </c>
+      <c r="L124" s="22">
+        <v>17500</v>
+      </c>
+      <c r="M124" s="15">
+        <v>16500</v>
+      </c>
+      <c r="N124" s="23">
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="O124" s="24">
+        <v>0.61499999999999999</v>
+      </c>
+      <c r="P124" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="125" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A125" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="B125" s="13">
+        <v>27</v>
+      </c>
+      <c r="C125" s="14">
+        <v>24.5</v>
+      </c>
+      <c r="D125" s="16">
+        <v>1092</v>
+      </c>
+      <c r="E125" s="17">
+        <v>10756</v>
+      </c>
+      <c r="F125" s="18">
+        <v>2.4</v>
+      </c>
+      <c r="G125">
+        <v>2</v>
+      </c>
+      <c r="H125" s="19">
+        <v>5.7</v>
+      </c>
+      <c r="I125" s="15">
+        <v>5.7</v>
+      </c>
+      <c r="J125" s="21">
+        <v>14.3</v>
+      </c>
+      <c r="K125" s="15">
+        <v>14.3</v>
+      </c>
+      <c r="L125" s="22">
+        <v>17500</v>
+      </c>
+      <c r="M125" s="15">
+        <v>16500</v>
+      </c>
+      <c r="N125" s="23">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="O125" s="24">
+        <v>0.66</v>
+      </c>
+      <c r="P125" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="126" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A126" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="B126" s="13">
+        <v>27.5</v>
+      </c>
+      <c r="C126" s="14">
+        <v>24.5</v>
+      </c>
+      <c r="D126" s="16">
+        <v>1030</v>
+      </c>
+      <c r="E126" s="17">
+        <v>10756</v>
+      </c>
+      <c r="F126" s="18">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="G126">
+        <v>2</v>
+      </c>
+      <c r="H126" s="19">
+        <v>6.2</v>
+      </c>
+      <c r="I126" s="15">
+        <v>5.7</v>
+      </c>
+      <c r="J126" s="21">
+        <v>14</v>
+      </c>
+      <c r="K126" s="15">
+        <v>14.3</v>
+      </c>
+      <c r="L126" s="22">
+        <v>17550</v>
+      </c>
+      <c r="M126" s="15">
+        <v>16500</v>
+      </c>
+      <c r="N126" s="23">
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="O126" s="24">
+        <v>0.64599999999999991</v>
+      </c>
+      <c r="P126" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="127" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A127" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="B127" s="13">
+        <v>20</v>
+      </c>
+      <c r="C127" s="14">
+        <v>24.5</v>
+      </c>
+      <c r="D127" s="16">
+        <v>194</v>
+      </c>
+      <c r="E127" s="17">
+        <v>10756</v>
+      </c>
+      <c r="F127" s="18">
+        <v>3.1</v>
+      </c>
+      <c r="G127">
+        <v>2</v>
+      </c>
+      <c r="H127" s="19">
+        <v>3.5</v>
+      </c>
+      <c r="I127" s="15">
+        <v>5.7</v>
+      </c>
+      <c r="J127" s="21">
+        <v>17.399999999999999</v>
+      </c>
+      <c r="K127" s="15">
+        <v>14.3</v>
+      </c>
+      <c r="L127" s="22">
+        <v>14000</v>
+      </c>
+      <c r="M127" s="15">
+        <v>16500</v>
+      </c>
+      <c r="N127" s="23">
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="O127" s="24">
+        <v>0.624</v>
+      </c>
+      <c r="P127" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="128" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A128" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="B128" s="13">
+        <v>19.5</v>
+      </c>
+      <c r="C128" s="14">
+        <v>24.5</v>
+      </c>
+      <c r="D128" s="16">
+        <v>121</v>
+      </c>
+      <c r="E128" s="17">
+        <v>10756</v>
+      </c>
+      <c r="F128" s="18">
+        <v>5.6</v>
+      </c>
+      <c r="G128">
+        <v>2</v>
+      </c>
+      <c r="H128" s="19">
+        <v>3</v>
+      </c>
+      <c r="I128" s="15">
+        <v>5.7</v>
+      </c>
+      <c r="J128" s="21">
+        <v>17</v>
+      </c>
+      <c r="K128" s="15">
+        <v>14.3</v>
+      </c>
+      <c r="L128" s="22">
+        <v>14000</v>
+      </c>
+      <c r="M128" s="15">
+        <v>16500</v>
+      </c>
+      <c r="N128" s="23">
+        <v>0.67</v>
+      </c>
+      <c r="O128" s="24">
+        <v>0.79599999999999993</v>
+      </c>
+      <c r="P128" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="129" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A129" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="B129" s="13">
+        <v>19.5</v>
+      </c>
+      <c r="C129" s="14">
+        <v>24.5</v>
+      </c>
+      <c r="D129" s="16">
+        <v>110</v>
+      </c>
+      <c r="E129" s="17">
+        <v>10756</v>
+      </c>
+      <c r="F129" s="18">
+        <v>5.6</v>
+      </c>
+      <c r="G129">
+        <v>2</v>
+      </c>
+      <c r="H129" s="19">
+        <v>3</v>
+      </c>
+      <c r="I129" s="15">
+        <v>5.7</v>
+      </c>
+      <c r="J129" s="21">
+        <v>17</v>
+      </c>
+      <c r="K129" s="15">
+        <v>14.3</v>
+      </c>
+      <c r="L129" s="22">
+        <v>14000</v>
+      </c>
+      <c r="M129" s="15">
+        <v>16500</v>
+      </c>
+      <c r="N129" s="23">
+        <v>0.65</v>
+      </c>
+      <c r="O129" s="24">
+        <v>0.70599999999999996</v>
+      </c>
+      <c r="P129" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="130" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A130" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="B130" s="13">
+        <v>19.5</v>
+      </c>
+      <c r="C130" s="14">
+        <v>24.5</v>
+      </c>
+      <c r="D130" s="16">
+        <v>89</v>
+      </c>
+      <c r="E130" s="17">
+        <v>10756</v>
+      </c>
+      <c r="F130" s="18">
+        <v>3</v>
+      </c>
+      <c r="G130">
+        <v>2</v>
+      </c>
+      <c r="H130" s="19">
+        <v>3</v>
+      </c>
+      <c r="I130" s="15">
+        <v>5.7</v>
+      </c>
+      <c r="J130" s="21">
+        <v>18</v>
+      </c>
+      <c r="K130" s="15">
+        <v>14.3</v>
+      </c>
+      <c r="L130" s="22">
+        <v>14500</v>
+      </c>
+      <c r="M130" s="15">
+        <v>16500</v>
+      </c>
+      <c r="N130" s="23">
+        <v>0.61</v>
+      </c>
+      <c r="O130" s="24">
+        <v>0.60899999999999999</v>
+      </c>
+      <c r="P130" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="131" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A131" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="B131" s="25">
+        <v>19</v>
+      </c>
+      <c r="C131" s="14">
+        <v>19.5</v>
+      </c>
+      <c r="D131" s="26">
+        <v>2309</v>
+      </c>
+      <c r="E131" s="27">
+        <v>13345</v>
+      </c>
+      <c r="F131" s="28">
+        <v>5.6</v>
+      </c>
+      <c r="G131">
+        <v>7</v>
+      </c>
+      <c r="H131" s="29">
+        <v>3</v>
+      </c>
+      <c r="I131" s="15">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="J131" s="30">
+        <v>17</v>
+      </c>
+      <c r="K131" s="15">
+        <v>17.8</v>
+      </c>
+      <c r="L131" s="31">
+        <v>13000</v>
+      </c>
+      <c r="M131" s="15">
+        <v>14500</v>
+      </c>
+      <c r="N131" s="32">
+        <v>0.43</v>
+      </c>
+      <c r="O131" s="33">
+        <v>0.70599999999999996</v>
+      </c>
+      <c r="P131" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="132" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A132" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="B132" s="25">
+        <v>19.5</v>
+      </c>
+      <c r="C132" s="14">
+        <v>19.5</v>
+      </c>
+      <c r="D132" s="26">
+        <v>2146</v>
+      </c>
+      <c r="E132" s="27">
+        <v>13345</v>
+      </c>
+      <c r="F132" s="28">
+        <v>5.6</v>
+      </c>
+      <c r="G132">
+        <v>7</v>
+      </c>
+      <c r="H132" s="29">
+        <v>3</v>
+      </c>
+      <c r="I132" s="15">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="J132" s="30">
+        <v>17</v>
+      </c>
+      <c r="K132" s="15">
+        <v>17.8</v>
+      </c>
+      <c r="L132" s="31">
+        <v>14000</v>
+      </c>
+      <c r="M132" s="15">
+        <v>14500</v>
+      </c>
+      <c r="N132" s="32">
+        <v>0.5</v>
+      </c>
+      <c r="O132" s="33">
+        <v>0.79599999999999993</v>
+      </c>
+      <c r="P132" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="133" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A133" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="B133" s="25">
+        <v>19.5</v>
+      </c>
+      <c r="C133" s="14">
+        <v>19.5</v>
+      </c>
+      <c r="D133" s="26">
+        <v>1910</v>
+      </c>
+      <c r="E133" s="27">
+        <v>13345</v>
+      </c>
+      <c r="F133" s="28">
+        <v>5.6</v>
+      </c>
+      <c r="G133">
+        <v>7</v>
+      </c>
+      <c r="H133" s="29">
+        <v>3</v>
+      </c>
+      <c r="I133" s="15">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="J133" s="30">
+        <v>17</v>
+      </c>
+      <c r="K133" s="15">
+        <v>17.8</v>
+      </c>
+      <c r="L133" s="31">
+        <v>14000</v>
+      </c>
+      <c r="M133" s="15">
+        <v>14500</v>
+      </c>
+      <c r="N133" s="32">
+        <v>0.45</v>
+      </c>
+      <c r="O133" s="33">
+        <v>0.70599999999999996</v>
+      </c>
+      <c r="P133" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="134" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A134" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="B134" s="25">
+        <v>19.5</v>
+      </c>
+      <c r="C134" s="14">
+        <v>19.5</v>
+      </c>
+      <c r="D134" s="26">
+        <v>1811</v>
+      </c>
+      <c r="E134" s="27">
+        <v>13345</v>
+      </c>
+      <c r="F134" s="28">
+        <v>3</v>
+      </c>
+      <c r="G134">
+        <v>7</v>
+      </c>
+      <c r="H134" s="29">
+        <v>3</v>
+      </c>
+      <c r="I134" s="15">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="J134" s="30">
+        <v>18</v>
+      </c>
+      <c r="K134" s="15">
+        <v>17.8</v>
+      </c>
+      <c r="L134" s="31">
+        <v>14500</v>
+      </c>
+      <c r="M134" s="15">
+        <v>14500</v>
+      </c>
+      <c r="N134" s="32">
+        <v>0.43</v>
+      </c>
+      <c r="O134" s="33">
+        <v>0.60899999999999999</v>
+      </c>
+      <c r="P134" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="135" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A135" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="B135" s="25">
+        <v>19</v>
+      </c>
+      <c r="C135" s="14">
+        <v>19.5</v>
+      </c>
+      <c r="D135" s="26">
+        <v>1709</v>
+      </c>
+      <c r="E135" s="27">
+        <v>13345</v>
+      </c>
+      <c r="F135" s="28">
+        <v>3</v>
+      </c>
+      <c r="G135">
+        <v>7</v>
+      </c>
+      <c r="H135" s="29">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="I135" s="15">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="J135" s="30">
+        <v>17.8</v>
+      </c>
+      <c r="K135" s="15">
+        <v>17.8</v>
+      </c>
+      <c r="L135" s="31">
+        <v>14000</v>
+      </c>
+      <c r="M135" s="15">
+        <v>14500</v>
+      </c>
+      <c r="N135" s="32">
+        <v>0.37</v>
+      </c>
+      <c r="O135" s="33">
+        <v>0.60899999999999999</v>
+      </c>
+      <c r="P135" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="136" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A136" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="B136" s="25">
+        <v>20</v>
+      </c>
+      <c r="C136" s="14">
+        <v>19.5</v>
+      </c>
+      <c r="D136" s="26">
+        <v>1435</v>
+      </c>
+      <c r="E136" s="27">
+        <v>13345</v>
+      </c>
+      <c r="F136" s="28">
+        <v>3.1</v>
+      </c>
+      <c r="G136">
+        <v>7</v>
+      </c>
+      <c r="H136" s="29">
+        <v>3.5</v>
+      </c>
+      <c r="I136" s="15">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="J136" s="30">
+        <v>17.399999999999999</v>
+      </c>
+      <c r="K136" s="15">
+        <v>17.8</v>
+      </c>
+      <c r="L136" s="31">
+        <v>14000</v>
+      </c>
+      <c r="M136" s="15">
+        <v>14500</v>
+      </c>
+      <c r="N136" s="32">
+        <v>0.43</v>
+      </c>
+      <c r="O136" s="33">
+        <v>0.624</v>
+      </c>
+      <c r="P136" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="137" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A137" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="B137" s="25">
+        <v>21.75</v>
+      </c>
+      <c r="C137" s="14">
+        <v>19.5</v>
+      </c>
+      <c r="D137" s="26">
+        <v>1314</v>
+      </c>
+      <c r="E137" s="27">
+        <v>13345</v>
+      </c>
+      <c r="F137" s="28">
+        <v>2.9</v>
+      </c>
+      <c r="G137">
+        <v>7</v>
+      </c>
+      <c r="H137" s="29">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="I137" s="15">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="J137" s="30">
+        <v>17.8</v>
+      </c>
+      <c r="K137" s="15">
+        <v>17.8</v>
+      </c>
+      <c r="L137" s="31">
+        <v>13000</v>
+      </c>
+      <c r="M137" s="15">
+        <v>14500</v>
+      </c>
+      <c r="N137" s="32">
+        <v>0.34</v>
+      </c>
+      <c r="O137" s="33">
+        <v>0.76700000000000002</v>
+      </c>
+      <c r="P137" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="138" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A138" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="B138" s="25">
+        <v>24</v>
+      </c>
+      <c r="C138" s="14">
+        <v>19.5</v>
+      </c>
+      <c r="D138" s="26">
+        <v>697</v>
+      </c>
+      <c r="E138" s="27">
+        <v>13345</v>
+      </c>
+      <c r="F138" s="28">
+        <v>2.9</v>
+      </c>
+      <c r="G138">
+        <v>7</v>
+      </c>
+      <c r="H138" s="29">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="I138" s="15">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="J138" s="30">
+        <v>17.8</v>
+      </c>
+      <c r="K138" s="15">
+        <v>17.8</v>
+      </c>
+      <c r="L138" s="31">
+        <v>14000</v>
+      </c>
+      <c r="M138" s="15">
+        <v>14500</v>
+      </c>
+      <c r="N138" s="32">
+        <v>0.37</v>
+      </c>
+      <c r="O138" s="33">
+        <v>0.56100000000000005</v>
+      </c>
+      <c r="P138" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="139" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A139" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="B139" s="25">
+        <v>24.5</v>
+      </c>
+      <c r="C139" s="14">
+        <v>19.5</v>
+      </c>
+      <c r="D139" s="26">
+        <v>4</v>
+      </c>
+      <c r="E139" s="27">
+        <v>13345</v>
+      </c>
+      <c r="F139" s="28">
+        <v>2.4</v>
+      </c>
+      <c r="G139">
+        <v>7</v>
+      </c>
+      <c r="H139" s="29">
+        <v>5.9</v>
+      </c>
+      <c r="I139" s="15">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="J139" s="30">
+        <v>14.5</v>
+      </c>
+      <c r="K139" s="15">
+        <v>17.8</v>
+      </c>
+      <c r="L139" s="31">
+        <v>17500</v>
+      </c>
+      <c r="M139" s="15">
+        <v>14500</v>
+      </c>
+      <c r="N139" s="32">
+        <v>0.43</v>
+      </c>
+      <c r="O139" s="33">
+        <v>0.61499999999999999</v>
+      </c>
+      <c r="P139" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="140" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A140" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="B140" s="25">
+        <v>27.5</v>
+      </c>
+      <c r="C140" s="14">
+        <v>19.5</v>
+      </c>
+      <c r="D140" s="26">
+        <v>2</v>
+      </c>
+      <c r="E140" s="27">
+        <v>13345</v>
+      </c>
+      <c r="F140" s="28">
+        <v>2.4</v>
+      </c>
+      <c r="G140">
+        <v>7</v>
+      </c>
+      <c r="H140" s="29">
+        <v>5.7</v>
+      </c>
+      <c r="I140" s="15">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="J140" s="30">
+        <v>14.3</v>
+      </c>
+      <c r="K140" s="15">
+        <v>17.8</v>
+      </c>
+      <c r="L140" s="31">
+        <v>17500</v>
+      </c>
+      <c r="M140" s="15">
+        <v>14500</v>
+      </c>
+      <c r="N140" s="32">
+        <v>0.45</v>
+      </c>
+      <c r="O140" s="33">
+        <v>0.75</v>
+      </c>
+      <c r="P140" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="141" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A141" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="B141" s="25">
+        <v>27.75</v>
+      </c>
+      <c r="C141" s="14">
+        <v>19.5</v>
+      </c>
+      <c r="D141" s="26">
+        <v>2</v>
+      </c>
+      <c r="E141" s="27">
+        <v>13345</v>
+      </c>
+      <c r="F141" s="28">
+        <v>2.4</v>
+      </c>
+      <c r="G141">
+        <v>7</v>
+      </c>
+      <c r="H141" s="29">
+        <v>5.7</v>
+      </c>
+      <c r="I141" s="15">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="J141" s="30">
+        <v>14.3</v>
+      </c>
+      <c r="K141" s="15">
+        <v>17.8</v>
+      </c>
+      <c r="L141" s="31">
+        <v>18000</v>
+      </c>
+      <c r="M141" s="15">
+        <v>14500</v>
+      </c>
+      <c r="N141" s="32">
+        <v>0.43</v>
+      </c>
+      <c r="O141" s="33">
+        <v>0.81700000000000006</v>
+      </c>
+      <c r="P141" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="142" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A142" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="B142" s="25">
+        <v>26.5</v>
+      </c>
+      <c r="C142" s="14">
+        <v>19.5</v>
+      </c>
+      <c r="D142" s="26">
+        <v>2</v>
+      </c>
+      <c r="E142" s="27">
+        <v>13345</v>
+      </c>
+      <c r="F142" s="28">
+        <v>2.4</v>
+      </c>
+      <c r="G142">
+        <v>7</v>
+      </c>
+      <c r="H142" s="29">
+        <v>5.7</v>
+      </c>
+      <c r="I142" s="15">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="J142" s="30">
+        <v>14.3</v>
+      </c>
+      <c r="K142" s="15">
+        <v>17.8</v>
+      </c>
+      <c r="L142" s="31">
+        <v>17500</v>
+      </c>
+      <c r="M142" s="15">
+        <v>14500</v>
+      </c>
+      <c r="N142" s="32">
+        <v>0.5</v>
+      </c>
+      <c r="O142" s="33">
+        <v>0.81700000000000006</v>
+      </c>
+      <c r="P142" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="143" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A143" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="B143" s="34">
+        <v>39.5</v>
+      </c>
+      <c r="C143" s="14">
+        <v>34.5</v>
+      </c>
+      <c r="D143" s="35">
+        <v>516</v>
+      </c>
+      <c r="E143" s="36">
+        <v>3956</v>
+      </c>
+      <c r="F143" s="37">
+        <v>1.4</v>
+      </c>
+      <c r="G143">
+        <v>0.5</v>
+      </c>
+      <c r="H143" s="38">
+        <v>9.3000000000000007</v>
+      </c>
+      <c r="I143" s="15">
+        <v>9.8000000000000007</v>
+      </c>
+      <c r="J143" s="39">
+        <v>10.9</v>
+      </c>
+      <c r="K143" s="15">
+        <v>10.199999999999999</v>
+      </c>
+      <c r="L143" s="40">
+        <v>23500</v>
+      </c>
+      <c r="M143" s="15">
+        <v>22500</v>
+      </c>
+      <c r="N143" s="41">
+        <v>0.6</v>
+      </c>
+      <c r="O143" s="42">
+        <v>0.77400000000000002</v>
+      </c>
+      <c r="P143" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="144" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A144" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="B144" s="34">
+        <v>39.5</v>
+      </c>
+      <c r="C144" s="14">
+        <v>34.5</v>
+      </c>
+      <c r="D144" s="35">
+        <v>507</v>
+      </c>
+      <c r="E144" s="36">
+        <v>3956</v>
+      </c>
+      <c r="F144" s="37">
+        <v>1.4</v>
+      </c>
+      <c r="G144">
+        <v>0.5</v>
+      </c>
+      <c r="H144" s="38">
+        <v>9</v>
+      </c>
+      <c r="I144" s="15">
+        <v>9.8000000000000007</v>
+      </c>
+      <c r="J144" s="39">
+        <v>11</v>
+      </c>
+      <c r="K144" s="15">
+        <v>10.199999999999999</v>
+      </c>
+      <c r="L144" s="40">
+        <v>22000</v>
+      </c>
+      <c r="M144" s="15">
+        <v>22500</v>
+      </c>
+      <c r="N144" s="41">
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="O144" s="42">
+        <v>0.65900000000000003</v>
+      </c>
+      <c r="P144" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="145" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A145" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="B145" s="34">
+        <v>38</v>
+      </c>
+      <c r="C145" s="14">
+        <v>34.5</v>
+      </c>
+      <c r="D145" s="35">
+        <v>486</v>
+      </c>
+      <c r="E145" s="36">
+        <v>3956</v>
+      </c>
+      <c r="F145" s="37">
+        <v>1.5</v>
+      </c>
+      <c r="G145">
+        <v>0.5</v>
+      </c>
+      <c r="H145" s="38">
+        <v>8.9</v>
+      </c>
+      <c r="I145" s="15">
+        <v>9.8000000000000007</v>
+      </c>
+      <c r="J145" s="39">
+        <v>11.3</v>
+      </c>
+      <c r="K145" s="15">
+        <v>10.199999999999999</v>
+      </c>
+      <c r="L145" s="40">
+        <v>23000</v>
+      </c>
+      <c r="M145" s="15">
+        <v>22500</v>
+      </c>
+      <c r="N145" s="41">
+        <v>0.5</v>
+      </c>
+      <c r="O145" s="42">
+        <v>0.50800000000000001</v>
+      </c>
+      <c r="P145" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="146" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A146" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="B146" s="34">
+        <v>39.5</v>
+      </c>
+      <c r="C146" s="14">
+        <v>34.5</v>
+      </c>
+      <c r="D146" s="35">
+        <v>475</v>
+      </c>
+      <c r="E146" s="36">
+        <v>3956</v>
+      </c>
+      <c r="F146" s="37">
+        <v>1.4</v>
+      </c>
+      <c r="G146">
+        <v>0.5</v>
+      </c>
+      <c r="H146" s="38">
+        <v>9.1</v>
+      </c>
+      <c r="I146" s="15">
+        <v>9.8000000000000007</v>
+      </c>
+      <c r="J146" s="39">
+        <v>11</v>
+      </c>
+      <c r="K146" s="15">
+        <v>10.199999999999999</v>
+      </c>
+      <c r="L146" s="40">
+        <v>22500</v>
+      </c>
+      <c r="M146" s="15">
+        <v>22500</v>
+      </c>
+      <c r="N146" s="41">
+        <v>0.5</v>
+      </c>
+      <c r="O146" s="42">
+        <v>0.60299999999999998</v>
+      </c>
+      <c r="P146" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="147" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A147" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="B147" s="34">
+        <v>36.5</v>
+      </c>
+      <c r="C147" s="14">
+        <v>34.5</v>
+      </c>
+      <c r="D147" s="35">
+        <v>429</v>
+      </c>
+      <c r="E147" s="36">
+        <v>3956</v>
+      </c>
+      <c r="F147" s="37">
+        <v>2.7</v>
+      </c>
+      <c r="G147">
+        <v>0.5</v>
+      </c>
+      <c r="H147" s="38">
+        <v>8</v>
+      </c>
+      <c r="I147" s="15">
+        <v>9.8000000000000007</v>
+      </c>
+      <c r="J147" s="39">
+        <v>12</v>
+      </c>
+      <c r="K147" s="15">
+        <v>10.199999999999999</v>
+      </c>
+      <c r="L147" s="40">
+        <v>23000</v>
+      </c>
+      <c r="M147" s="15">
+        <v>22500</v>
+      </c>
+      <c r="N147" s="41">
+        <v>0.5</v>
+      </c>
+      <c r="O147" s="42">
+        <v>0.60299999999999998</v>
+      </c>
+      <c r="P147" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="148" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A148" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="B148" s="34">
+        <v>39.5</v>
+      </c>
+      <c r="C148" s="14">
+        <v>34.5</v>
+      </c>
+      <c r="D148" s="35">
+        <v>426</v>
+      </c>
+      <c r="E148" s="36">
+        <v>3956</v>
+      </c>
+      <c r="F148" s="37">
+        <v>1.6</v>
+      </c>
+      <c r="G148">
+        <v>0.5</v>
+      </c>
+      <c r="H148" s="38">
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="I148" s="15">
+        <v>9.8000000000000007</v>
+      </c>
+      <c r="J148" s="39">
+        <v>11.5</v>
+      </c>
+      <c r="K148" s="15">
+        <v>10.199999999999999</v>
+      </c>
+      <c r="L148" s="40">
+        <v>23000</v>
+      </c>
+      <c r="M148" s="15">
+        <v>22500</v>
+      </c>
+      <c r="N148" s="41">
+        <v>0.46</v>
+      </c>
+      <c r="O148" s="42">
+        <v>0.52400000000000002</v>
+      </c>
+      <c r="P148" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="149" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A149" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="B149" s="34">
+        <v>39.25</v>
+      </c>
+      <c r="C149" s="14">
+        <v>34.5</v>
+      </c>
+      <c r="D149" s="35">
+        <v>344</v>
+      </c>
+      <c r="E149" s="36">
+        <v>3956</v>
+      </c>
+      <c r="F149" s="37">
+        <v>2.7</v>
+      </c>
+      <c r="G149">
+        <v>0.5</v>
+      </c>
+      <c r="H149" s="38">
+        <v>8</v>
+      </c>
+      <c r="I149" s="15">
+        <v>9.8000000000000007</v>
+      </c>
+      <c r="J149" s="39">
+        <v>12</v>
+      </c>
+      <c r="K149" s="15">
+        <v>10.199999999999999</v>
+      </c>
+      <c r="L149" s="40">
+        <v>23000</v>
+      </c>
+      <c r="M149" s="15">
+        <v>22500</v>
+      </c>
+      <c r="N149" s="41">
+        <v>0.43</v>
+      </c>
+      <c r="O149" s="42">
+        <v>0.52400000000000002</v>
+      </c>
+      <c r="P149" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="150" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A150" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="B150" s="34">
+        <v>38</v>
+      </c>
+      <c r="C150" s="14">
+        <v>34.5</v>
+      </c>
+      <c r="D150" s="35">
+        <v>343</v>
+      </c>
+      <c r="E150" s="36">
+        <v>3956</v>
+      </c>
+      <c r="F150" s="37">
+        <v>2.7</v>
+      </c>
+      <c r="G150">
+        <v>0.5</v>
+      </c>
+      <c r="H150" s="38">
+        <v>8</v>
+      </c>
+      <c r="I150" s="15">
+        <v>9.8000000000000007</v>
+      </c>
+      <c r="J150" s="39">
+        <v>12</v>
+      </c>
+      <c r="K150" s="15">
+        <v>10.199999999999999</v>
+      </c>
+      <c r="L150" s="40">
+        <v>23000</v>
+      </c>
+      <c r="M150" s="15">
+        <v>22500</v>
+      </c>
+      <c r="N150" s="41">
+        <v>0.42</v>
+      </c>
+      <c r="O150" s="42">
+        <v>0.47600000000000003</v>
+      </c>
+      <c r="P150" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="151" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A151" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="B151" s="34">
+        <v>32.5</v>
+      </c>
+      <c r="C151" s="14">
+        <v>34.5</v>
+      </c>
+      <c r="D151" s="35">
+        <v>65</v>
+      </c>
+      <c r="E151" s="36">
+        <v>3956</v>
+      </c>
+      <c r="F151" s="37">
+        <v>2</v>
+      </c>
+      <c r="G151">
+        <v>0.5</v>
+      </c>
+      <c r="H151" s="38">
+        <v>10</v>
+      </c>
+      <c r="I151" s="15">
+        <v>9.8000000000000007</v>
+      </c>
+      <c r="J151" s="39">
+        <v>15</v>
+      </c>
+      <c r="K151" s="15">
+        <v>10.199999999999999</v>
+      </c>
+      <c r="L151" s="40">
+        <v>26000</v>
+      </c>
+      <c r="M151" s="15">
+        <v>22500</v>
+      </c>
+      <c r="N151" s="41">
+        <v>0.5</v>
+      </c>
+      <c r="O151" s="42">
+        <v>0.47100000000000003</v>
+      </c>
+      <c r="P151" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="152" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A152" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="B152" s="34">
+        <v>34.5</v>
+      </c>
+      <c r="C152" s="14">
+        <v>34.5</v>
+      </c>
+      <c r="D152" s="35">
+        <v>44</v>
+      </c>
+      <c r="E152" s="36">
+        <v>3956</v>
+      </c>
+      <c r="F152" s="37">
+        <v>1.9</v>
+      </c>
+      <c r="G152">
+        <v>0.5</v>
+      </c>
+      <c r="H152" s="38">
+        <v>10.4</v>
+      </c>
+      <c r="I152" s="15">
+        <v>9.8000000000000007</v>
+      </c>
+      <c r="J152" s="39">
+        <v>14.8</v>
+      </c>
+      <c r="K152" s="15">
+        <v>10.199999999999999</v>
+      </c>
+      <c r="L152" s="40">
+        <v>27000</v>
+      </c>
+      <c r="M152" s="15">
+        <v>22500</v>
+      </c>
+      <c r="N152" s="41">
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="O152" s="42">
+        <v>0.55100000000000005</v>
+      </c>
+      <c r="P152" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="153" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A153" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="B153" s="34">
+        <v>34</v>
+      </c>
+      <c r="C153" s="14">
+        <v>34.5</v>
+      </c>
+      <c r="D153" s="35">
+        <v>33</v>
+      </c>
+      <c r="E153" s="36">
+        <v>3956</v>
+      </c>
+      <c r="F153" s="37">
+        <v>2.1</v>
+      </c>
+      <c r="G153">
+        <v>0.5</v>
+      </c>
+      <c r="H153" s="38">
+        <v>9.9</v>
+      </c>
+      <c r="I153" s="15">
+        <v>9.8000000000000007</v>
+      </c>
+      <c r="J153" s="39">
+        <v>15.3</v>
+      </c>
+      <c r="K153" s="15">
+        <v>10.199999999999999</v>
+      </c>
+      <c r="L153" s="40">
+        <v>25000</v>
+      </c>
+      <c r="M153" s="15">
+        <v>22500</v>
+      </c>
+      <c r="N153" s="41">
+        <v>0.46</v>
+      </c>
+      <c r="O153" s="42">
+        <v>0.48700000000000004</v>
+      </c>
+      <c r="P153" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="154" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A154" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="B154" s="34">
+        <v>29.75</v>
+      </c>
+      <c r="C154" s="14">
+        <v>34.5</v>
+      </c>
+      <c r="D154" s="35">
+        <v>32</v>
+      </c>
+      <c r="E154" s="36">
+        <v>3956</v>
+      </c>
+      <c r="F154" s="37">
+        <v>2.4</v>
+      </c>
+      <c r="G154">
+        <v>0.5</v>
+      </c>
+      <c r="H154" s="38">
+        <v>6</v>
+      </c>
+      <c r="I154" s="15">
+        <v>9.8000000000000007</v>
+      </c>
+      <c r="J154" s="39">
+        <v>14.2</v>
+      </c>
+      <c r="K154" s="15">
+        <v>10.199999999999999</v>
+      </c>
+      <c r="L154" s="40">
+        <v>17000</v>
+      </c>
+      <c r="M154" s="15">
+        <v>22500</v>
+      </c>
+      <c r="N154" s="41">
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="O154" s="42">
+        <v>0.80400000000000005</v>
+      </c>
+      <c r="P154" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="155" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A155" t="s">
+        <v>6</v>
+      </c>
+      <c r="B155" s="43">
+        <v>34</v>
+      </c>
+      <c r="C155" s="14">
+        <v>29.5</v>
+      </c>
+      <c r="D155" s="44">
+        <v>544</v>
+      </c>
+      <c r="E155" s="45">
+        <v>3059</v>
+      </c>
+      <c r="F155" s="46">
+        <v>1.9</v>
+      </c>
+      <c r="G155">
+        <v>1</v>
+      </c>
+      <c r="H155" s="47">
+        <v>10.4</v>
+      </c>
+      <c r="I155" s="15">
+        <v>10.4</v>
+      </c>
+      <c r="J155" s="48">
+        <v>15.3</v>
+      </c>
+      <c r="K155" s="15">
+        <v>15.3</v>
+      </c>
+      <c r="L155" s="49">
+        <v>27000</v>
+      </c>
+      <c r="M155" s="15">
+        <v>24500</v>
+      </c>
+      <c r="N155" s="50">
+        <v>0.48</v>
+      </c>
+      <c r="O155" s="51">
+        <v>0.754</v>
+      </c>
+      <c r="P155" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="156" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A156" t="s">
+        <v>6</v>
+      </c>
+      <c r="B156" s="43">
+        <v>33.25</v>
+      </c>
+      <c r="C156" s="14">
+        <v>29.5</v>
+      </c>
+      <c r="D156" s="44">
+        <v>396</v>
+      </c>
+      <c r="E156" s="45">
+        <v>3059</v>
+      </c>
+      <c r="F156" s="46">
+        <v>2</v>
+      </c>
+      <c r="G156">
+        <v>1</v>
+      </c>
+      <c r="H156" s="47">
+        <v>10.4</v>
+      </c>
+      <c r="I156" s="15">
+        <v>10.4</v>
+      </c>
+      <c r="J156" s="48">
+        <v>15.3</v>
+      </c>
+      <c r="K156" s="15">
+        <v>15.3</v>
+      </c>
+      <c r="L156" s="49">
+        <v>25000</v>
+      </c>
+      <c r="M156" s="15">
+        <v>24500</v>
+      </c>
+      <c r="N156" s="50">
+        <v>0.4</v>
+      </c>
+      <c r="O156" s="51">
+        <v>0.58200000000000007</v>
+      </c>
+      <c r="P156" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="157" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A157" t="s">
+        <v>6</v>
+      </c>
+      <c r="B157" s="43">
+        <v>32.5</v>
+      </c>
+      <c r="C157" s="14">
+        <v>29.5</v>
+      </c>
+      <c r="D157" s="44">
+        <v>391</v>
+      </c>
+      <c r="E157" s="45">
+        <v>3059</v>
+      </c>
+      <c r="F157" s="46">
+        <v>2</v>
+      </c>
+      <c r="G157">
+        <v>1</v>
+      </c>
+      <c r="H157" s="47">
+        <v>10</v>
+      </c>
+      <c r="I157" s="15">
+        <v>10.4</v>
+      </c>
+      <c r="J157" s="48">
+        <v>15</v>
+      </c>
+      <c r="K157" s="15">
+        <v>15.3</v>
+      </c>
+      <c r="L157" s="49">
+        <v>26000</v>
+      </c>
+      <c r="M157" s="15">
+        <v>24500</v>
+      </c>
+      <c r="N157" s="50">
+        <v>0.3</v>
+      </c>
+      <c r="O157" s="51">
+        <v>0.47100000000000003</v>
+      </c>
+      <c r="P157" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="158" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A158" t="s">
+        <v>6</v>
+      </c>
+      <c r="B158" s="43">
+        <v>33</v>
+      </c>
+      <c r="C158" s="14">
+        <v>29.5</v>
+      </c>
+      <c r="D158" s="44">
+        <v>378</v>
+      </c>
+      <c r="E158" s="45">
+        <v>3059</v>
+      </c>
+      <c r="F158" s="46">
+        <v>1.9</v>
+      </c>
+      <c r="G158">
+        <v>1</v>
+      </c>
+      <c r="H158" s="47">
+        <v>10.6</v>
+      </c>
+      <c r="I158" s="15">
+        <v>10.4</v>
+      </c>
+      <c r="J158" s="48">
+        <v>15.3</v>
+      </c>
+      <c r="K158" s="15">
+        <v>15.3</v>
+      </c>
+      <c r="L158" s="49">
+        <v>27000</v>
+      </c>
+      <c r="M158" s="15">
+        <v>24500</v>
+      </c>
+      <c r="N158" s="50">
+        <v>0.33</v>
+      </c>
+      <c r="O158" s="51">
+        <v>0.503</v>
+      </c>
+      <c r="P158" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="159" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A159" t="s">
+        <v>6</v>
+      </c>
+      <c r="B159" s="43">
+        <v>34.5</v>
+      </c>
+      <c r="C159" s="14">
+        <v>29.5</v>
+      </c>
+      <c r="D159" s="44">
+        <v>373</v>
+      </c>
+      <c r="E159" s="45">
+        <v>3059</v>
+      </c>
+      <c r="F159" s="46">
+        <v>1.9</v>
+      </c>
+      <c r="G159">
+        <v>1</v>
+      </c>
+      <c r="H159" s="47">
+        <v>10.4</v>
+      </c>
+      <c r="I159" s="15">
+        <v>10.4</v>
+      </c>
+      <c r="J159" s="48">
+        <v>14.8</v>
+      </c>
+      <c r="K159" s="15">
+        <v>15.3</v>
+      </c>
+      <c r="L159" s="49">
+        <v>27000</v>
+      </c>
+      <c r="M159" s="15">
+        <v>24500</v>
+      </c>
+      <c r="N159" s="50">
+        <v>0.37</v>
+      </c>
+      <c r="O159" s="51">
+        <v>0.55100000000000005</v>
+      </c>
+      <c r="P159" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="160" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A160" t="s">
+        <v>6</v>
+      </c>
+      <c r="B160" s="43">
+        <v>33</v>
+      </c>
+      <c r="C160" s="14">
+        <v>29.5</v>
+      </c>
+      <c r="D160" s="44">
+        <v>336</v>
+      </c>
+      <c r="E160" s="45">
+        <v>3059</v>
+      </c>
+      <c r="F160" s="46">
+        <v>2.1</v>
+      </c>
+      <c r="G160">
+        <v>1</v>
+      </c>
+      <c r="H160" s="47">
+        <v>10</v>
+      </c>
+      <c r="I160" s="15">
+        <v>10.4</v>
+      </c>
+      <c r="J160" s="48">
+        <v>15.3</v>
+      </c>
+      <c r="K160" s="15">
+        <v>15.3</v>
+      </c>
+      <c r="L160" s="49">
+        <v>25000</v>
+      </c>
+      <c r="M160" s="15">
+        <v>24500</v>
+      </c>
+      <c r="N160" s="50">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="O160" s="51">
+        <v>0.42499999999999999</v>
+      </c>
+      <c r="P160" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="161" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A161" t="s">
+        <v>6</v>
+      </c>
+      <c r="B161" s="43">
+        <v>34</v>
+      </c>
+      <c r="C161" s="14">
+        <v>29.5</v>
+      </c>
+      <c r="D161" s="44">
+        <v>336</v>
+      </c>
+      <c r="E161" s="45">
+        <v>3059</v>
+      </c>
+      <c r="F161" s="46">
+        <v>2.1</v>
+      </c>
+      <c r="G161">
+        <v>1</v>
+      </c>
+      <c r="H161" s="47">
+        <v>9.9</v>
+      </c>
+      <c r="I161" s="15">
+        <v>10.4</v>
+      </c>
+      <c r="J161" s="48">
+        <v>15.3</v>
+      </c>
+      <c r="K161" s="15">
+        <v>15.3</v>
+      </c>
+      <c r="L161" s="49">
+        <v>25000</v>
+      </c>
+      <c r="M161" s="15">
+        <v>24500</v>
+      </c>
+      <c r="N161" s="50">
+        <v>0.3</v>
+      </c>
+      <c r="O161" s="51">
+        <v>0.48700000000000004</v>
+      </c>
+      <c r="P161" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="162" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A162" t="s">
+        <v>6</v>
+      </c>
+      <c r="B162" s="43">
+        <v>33</v>
+      </c>
+      <c r="C162" s="14">
+        <v>29.5</v>
+      </c>
+      <c r="D162" s="44">
+        <v>289</v>
+      </c>
+      <c r="E162" s="45">
+        <v>3059</v>
+      </c>
+      <c r="F162" s="46">
+        <v>3.5</v>
+      </c>
+      <c r="G162">
+        <v>1</v>
+      </c>
+      <c r="H162" s="47">
+        <v>9.4</v>
+      </c>
+      <c r="I162" s="15">
+        <v>10.4</v>
+      </c>
+      <c r="J162" s="48">
+        <v>15.5</v>
+      </c>
+      <c r="K162" s="15">
+        <v>15.3</v>
+      </c>
+      <c r="L162" s="49">
+        <v>25000</v>
+      </c>
+      <c r="M162" s="15">
+        <v>24500</v>
+      </c>
+      <c r="N162" s="50">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="O162" s="51">
+        <v>0.42499999999999999</v>
+      </c>
+      <c r="P162" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="163" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A163" t="s">
+        <v>6</v>
+      </c>
+      <c r="B163" s="43">
+        <v>27.75</v>
+      </c>
+      <c r="C163" s="14">
+        <v>29.5</v>
+      </c>
+      <c r="D163" s="44">
+        <v>3</v>
+      </c>
+      <c r="E163" s="45">
+        <v>3059</v>
+      </c>
+      <c r="F163" s="46">
+        <v>2.4</v>
+      </c>
+      <c r="G163">
+        <v>1</v>
+      </c>
+      <c r="H163" s="47">
+        <v>5.7</v>
+      </c>
+      <c r="I163" s="15">
+        <v>10.4</v>
+      </c>
+      <c r="J163" s="48">
+        <v>14.3</v>
+      </c>
+      <c r="K163" s="15">
+        <v>15.3</v>
+      </c>
+      <c r="L163" s="49">
+        <v>18000</v>
+      </c>
+      <c r="M163" s="15">
+        <v>24500</v>
+      </c>
+      <c r="N163" s="50">
+        <v>0.4</v>
+      </c>
+      <c r="O163" s="51">
+        <v>0.81700000000000006</v>
+      </c>
+      <c r="P163" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="164" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A164" t="s">
+        <v>6</v>
+      </c>
+      <c r="B164" s="43">
+        <v>24.5</v>
+      </c>
+      <c r="C164" s="14">
+        <v>29.5</v>
+      </c>
+      <c r="D164" s="44">
+        <v>3</v>
+      </c>
+      <c r="E164" s="45">
+        <v>3059</v>
+      </c>
+      <c r="F164" s="46">
+        <v>2.4</v>
+      </c>
+      <c r="G164">
+        <v>1</v>
+      </c>
+      <c r="H164" s="47">
+        <v>5.9</v>
+      </c>
+      <c r="I164" s="15">
+        <v>10.4</v>
+      </c>
+      <c r="J164" s="48">
+        <v>14.5</v>
+      </c>
+      <c r="K164" s="15">
+        <v>15.3</v>
+      </c>
+      <c r="L164" s="49">
+        <v>17500</v>
+      </c>
+      <c r="M164" s="15">
+        <v>24500</v>
+      </c>
+      <c r="N164" s="50">
+        <v>0.33</v>
+      </c>
+      <c r="O164" s="51">
+        <v>0.61499999999999999</v>
+      </c>
+      <c r="P164" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="165" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A165" t="s">
+        <v>6</v>
+      </c>
+      <c r="B165" s="43">
+        <v>27.5</v>
+      </c>
+      <c r="C165" s="14">
+        <v>29.5</v>
+      </c>
+      <c r="D165" s="44">
+        <v>2</v>
+      </c>
+      <c r="E165" s="45">
+        <v>3059</v>
+      </c>
+      <c r="F165" s="46">
+        <v>2.4</v>
+      </c>
+      <c r="G165">
+        <v>1</v>
+      </c>
+      <c r="H165" s="47">
+        <v>5.7</v>
+      </c>
+      <c r="I165" s="15">
+        <v>10.4</v>
+      </c>
+      <c r="J165" s="48">
+        <v>14.3</v>
+      </c>
+      <c r="K165" s="15">
+        <v>15.3</v>
+      </c>
+      <c r="L165" s="49">
+        <v>17500</v>
+      </c>
+      <c r="M165" s="15">
+        <v>24500</v>
+      </c>
+      <c r="N165" s="50">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="O165" s="51">
+        <v>0.75</v>
+      </c>
+      <c r="P165" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="166" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A166" t="s">
+        <v>6</v>
+      </c>
+      <c r="B166" s="43">
+        <v>27.5</v>
+      </c>
+      <c r="C166" s="14">
+        <v>29.5</v>
+      </c>
+      <c r="D166" s="44">
+        <v>2</v>
+      </c>
+      <c r="E166" s="45">
+        <v>3059</v>
+      </c>
+      <c r="F166" s="46">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="G166">
+        <v>1</v>
+      </c>
+      <c r="H166" s="47">
+        <v>6.2</v>
+      </c>
+      <c r="I166" s="15">
+        <v>10.4</v>
+      </c>
+      <c r="J166" s="48">
+        <v>14</v>
+      </c>
+      <c r="K166" s="15">
+        <v>15.3</v>
+      </c>
+      <c r="L166" s="49">
+        <v>17550</v>
+      </c>
+      <c r="M166" s="15">
+        <v>24500</v>
+      </c>
+      <c r="N166" s="50">
+        <v>0.3</v>
+      </c>
+      <c r="O166" s="51">
+        <v>0.64599999999999991</v>
+      </c>
+      <c r="P166" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="167" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A167" t="s">
+        <v>7</v>
+      </c>
+      <c r="B167" s="52">
+        <v>32.5</v>
+      </c>
+      <c r="C167" s="14">
+        <v>29.5</v>
+      </c>
+      <c r="D167" s="53">
+        <v>441</v>
+      </c>
+      <c r="E167" s="54">
+        <v>3129</v>
+      </c>
+      <c r="F167" s="55">
+        <v>2</v>
+      </c>
+      <c r="G167">
+        <v>1</v>
+      </c>
+      <c r="H167" s="56">
+        <v>4.5</v>
+      </c>
+      <c r="I167" s="15">
+        <v>4.7</v>
+      </c>
+      <c r="J167" s="57">
+        <v>10.199999999999999</v>
+      </c>
+      <c r="K167" s="15">
+        <v>9.6</v>
+      </c>
+      <c r="L167" s="58">
+        <v>19000</v>
+      </c>
+      <c r="M167" s="15">
+        <v>18500</v>
+      </c>
+      <c r="N167" s="59">
+        <v>0.36</v>
+      </c>
+      <c r="O167" s="60">
+        <v>0.48700000000000004</v>
+      </c>
+      <c r="P167" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="168" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A168" t="s">
+        <v>7</v>
+      </c>
+      <c r="B168" s="52">
+        <v>34.5</v>
+      </c>
+      <c r="C168" s="14">
+        <v>29.5</v>
+      </c>
+      <c r="D168" s="53">
+        <v>445</v>
+      </c>
+      <c r="E168" s="54">
+        <v>3129</v>
+      </c>
+      <c r="F168" s="55">
+        <v>2.1</v>
+      </c>
+      <c r="G168">
+        <v>1</v>
+      </c>
+      <c r="H168" s="56">
+        <v>4.5</v>
+      </c>
+      <c r="I168" s="15">
+        <v>4.7</v>
+      </c>
+      <c r="J168" s="57">
+        <v>10.5</v>
+      </c>
+      <c r="K168" s="15">
+        <v>9.6</v>
+      </c>
+      <c r="L168" s="58">
+        <v>19000</v>
+      </c>
+      <c r="M168" s="15">
+        <v>18500</v>
+      </c>
+      <c r="N168" s="59">
+        <v>0.38</v>
+      </c>
+      <c r="O168" s="60">
+        <v>0.47100000000000003</v>
+      </c>
+      <c r="P168" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="169" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A169" t="s">
+        <v>7</v>
+      </c>
+      <c r="B169" s="52">
+        <v>34.5</v>
+      </c>
+      <c r="C169" s="14">
+        <v>29.5</v>
+      </c>
+      <c r="D169" s="53">
+        <v>366</v>
+      </c>
+      <c r="E169" s="54">
+        <v>3129</v>
+      </c>
+      <c r="F169" s="55">
+        <v>1.8</v>
+      </c>
+      <c r="G169">
+        <v>1</v>
+      </c>
+      <c r="H169" s="56">
+        <v>4.7</v>
+      </c>
+      <c r="I169" s="15">
+        <v>4.7</v>
+      </c>
+      <c r="J169" s="57">
+        <v>9.6</v>
+      </c>
+      <c r="K169" s="15">
+        <v>9.6</v>
+      </c>
+      <c r="L169" s="58">
+        <v>21000</v>
+      </c>
+      <c r="M169" s="15">
+        <v>18500</v>
+      </c>
+      <c r="N169" s="59">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="O169" s="60">
+        <v>0.754</v>
+      </c>
+      <c r="P169" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="170" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A170" t="s">
+        <v>7</v>
+      </c>
+      <c r="B170" s="52">
+        <v>31.5</v>
+      </c>
+      <c r="C170" s="14">
+        <v>29.5</v>
+      </c>
+      <c r="D170" s="53">
+        <v>353</v>
+      </c>
+      <c r="E170" s="54">
+        <v>3129</v>
+      </c>
+      <c r="F170" s="55">
+        <v>1.9</v>
+      </c>
+      <c r="G170">
+        <v>1</v>
+      </c>
+      <c r="H170" s="56">
+        <v>5</v>
+      </c>
+      <c r="I170" s="15">
+        <v>4.7</v>
+      </c>
+      <c r="J170" s="57">
+        <v>10</v>
+      </c>
+      <c r="K170" s="15">
+        <v>9.6</v>
+      </c>
+      <c r="L170" s="58">
+        <v>19000</v>
+      </c>
+      <c r="M170" s="15">
+        <v>18500</v>
+      </c>
+      <c r="N170" s="59">
+        <v>0.39</v>
+      </c>
+      <c r="O170" s="60">
+        <v>0.503</v>
+      </c>
+      <c r="P170" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="171" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A171" t="s">
+        <v>7</v>
+      </c>
+      <c r="B171" s="52">
+        <v>33.5</v>
+      </c>
+      <c r="C171" s="14">
+        <v>29.5</v>
+      </c>
+      <c r="D171" s="53">
+        <v>342</v>
+      </c>
+      <c r="E171" s="54">
+        <v>3129</v>
+      </c>
+      <c r="F171" s="55">
+        <v>1.9</v>
+      </c>
+      <c r="G171">
+        <v>1</v>
+      </c>
+      <c r="H171" s="56">
+        <v>4.7</v>
+      </c>
+      <c r="I171" s="15">
+        <v>4.7</v>
+      </c>
+      <c r="J171" s="57">
+        <v>9.6</v>
+      </c>
+      <c r="K171" s="15">
+        <v>9.6</v>
+      </c>
+      <c r="L171" s="58">
+        <v>19000</v>
+      </c>
+      <c r="M171" s="15">
+        <v>18500</v>
+      </c>
+      <c r="N171" s="59">
+        <v>0.46</v>
+      </c>
+      <c r="O171" s="60">
+        <v>0.58200000000000007</v>
+      </c>
+      <c r="P171" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="172" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A172" t="s">
+        <v>7</v>
+      </c>
+      <c r="B172" s="52">
+        <v>34</v>
+      </c>
+      <c r="C172" s="14">
+        <v>29.5</v>
+      </c>
+      <c r="D172" s="53">
+        <v>326</v>
+      </c>
+      <c r="E172" s="54">
+        <v>3129</v>
+      </c>
+      <c r="F172" s="55">
+        <v>1.9</v>
+      </c>
+      <c r="G172">
+        <v>1</v>
+      </c>
+      <c r="H172" s="56">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="I172" s="15">
+        <v>4.7</v>
+      </c>
+      <c r="J172" s="57">
+        <v>9.6999999999999993</v>
+      </c>
+      <c r="K172" s="15">
+        <v>9.6</v>
+      </c>
+      <c r="L172" s="58">
+        <v>18250</v>
+      </c>
+      <c r="M172" s="15">
+        <v>18500</v>
+      </c>
+      <c r="N172" s="59">
+        <v>0.45</v>
+      </c>
+      <c r="O172" s="60">
+        <v>0.58200000000000007</v>
+      </c>
+      <c r="P172" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="173" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A173" t="s">
+        <v>7</v>
+      </c>
+      <c r="B173" s="52">
+        <v>34.25</v>
+      </c>
+      <c r="C173" s="14">
+        <v>29.5</v>
+      </c>
+      <c r="D173" s="53">
+        <v>314</v>
+      </c>
+      <c r="E173" s="54">
+        <v>3129</v>
+      </c>
+      <c r="F173" s="55">
+        <v>1.8</v>
+      </c>
+      <c r="G173">
+        <v>1</v>
+      </c>
+      <c r="H173" s="56">
+        <v>4.7</v>
+      </c>
+      <c r="I173" s="15">
+        <v>4.7</v>
+      </c>
+      <c r="J173" s="57">
+        <v>9.6</v>
+      </c>
+      <c r="K173" s="15">
+        <v>9.6</v>
+      </c>
+      <c r="L173" s="58">
+        <v>19000</v>
+      </c>
+      <c r="M173" s="15">
+        <v>18500</v>
+      </c>
+      <c r="N173" s="59">
+        <v>0.47</v>
+      </c>
+      <c r="O173" s="60">
+        <v>0.66400000000000003</v>
+      </c>
+      <c r="P173" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="174" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A174" t="s">
+        <v>7</v>
+      </c>
+      <c r="B174" s="52">
+        <v>33</v>
+      </c>
+      <c r="C174" s="14">
+        <v>29.5</v>
+      </c>
+      <c r="D174" s="53">
+        <v>300</v>
+      </c>
+      <c r="E174" s="54">
+        <v>3129</v>
+      </c>
+      <c r="F174" s="55">
+        <v>1.9</v>
+      </c>
+      <c r="G174">
+        <v>1</v>
+      </c>
+      <c r="H174" s="56">
+        <v>4.7</v>
+      </c>
+      <c r="I174" s="15">
+        <v>4.7</v>
+      </c>
+      <c r="J174" s="57">
+        <v>9.6</v>
+      </c>
+      <c r="K174" s="15">
+        <v>9.6</v>
+      </c>
+      <c r="L174" s="58">
+        <v>19000</v>
+      </c>
+      <c r="M174" s="15">
+        <v>18500</v>
+      </c>
+      <c r="N174" s="59">
+        <v>0.38</v>
+      </c>
+      <c r="O174" s="60">
+        <v>0.48700000000000004</v>
+      </c>
+      <c r="P174" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="175" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A175" t="s">
+        <v>7</v>
+      </c>
+      <c r="B175" s="52">
+        <v>27.75</v>
+      </c>
+      <c r="C175" s="14">
+        <v>29.5</v>
+      </c>
+      <c r="D175" s="53">
+        <v>43</v>
+      </c>
+      <c r="E175" s="54">
+        <v>3129</v>
+      </c>
+      <c r="F175" s="55">
+        <v>2.4</v>
+      </c>
+      <c r="G175">
+        <v>1</v>
+      </c>
+      <c r="H175" s="56">
+        <v>5.7</v>
+      </c>
+      <c r="I175" s="15">
+        <v>4.7</v>
+      </c>
+      <c r="J175" s="57">
+        <v>14.3</v>
+      </c>
+      <c r="K175" s="15">
+        <v>9.6</v>
+      </c>
+      <c r="L175" s="58">
+        <v>18000</v>
+      </c>
+      <c r="M175" s="15">
+        <v>18500</v>
+      </c>
+      <c r="N175" s="59">
+        <v>0.45</v>
+      </c>
+      <c r="O175" s="60">
+        <v>0.81700000000000006</v>
+      </c>
+      <c r="P175" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="176" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A176" t="s">
+        <v>7</v>
+      </c>
+      <c r="B176" s="52">
+        <v>27.5</v>
+      </c>
+      <c r="C176" s="14">
+        <v>29.5</v>
+      </c>
+      <c r="D176" s="53">
+        <v>39</v>
+      </c>
+      <c r="E176" s="54">
+        <v>3129</v>
+      </c>
+      <c r="F176" s="55">
+        <v>2.4</v>
+      </c>
+      <c r="G176">
+        <v>1</v>
+      </c>
+      <c r="H176" s="56">
+        <v>5.7</v>
+      </c>
+      <c r="I176" s="15">
+        <v>4.7</v>
+      </c>
+      <c r="J176" s="57">
+        <v>14.3</v>
+      </c>
+      <c r="K176" s="15">
+        <v>9.6</v>
+      </c>
+      <c r="L176" s="58">
+        <v>17500</v>
+      </c>
+      <c r="M176" s="15">
+        <v>18500</v>
+      </c>
+      <c r="N176" s="59">
+        <v>0.46</v>
+      </c>
+      <c r="O176" s="60">
+        <v>0.75</v>
+      </c>
+      <c r="P176" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="177" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A177" t="s">
+        <v>7</v>
+      </c>
+      <c r="B177" s="52">
+        <v>26.5</v>
+      </c>
+      <c r="C177" s="14">
+        <v>29.5</v>
+      </c>
+      <c r="D177" s="53">
+        <v>45</v>
+      </c>
+      <c r="E177" s="54">
+        <v>3129</v>
+      </c>
+      <c r="F177" s="55">
+        <v>2.4</v>
+      </c>
+      <c r="G177">
+        <v>1</v>
+      </c>
+      <c r="H177" s="56">
+        <v>5.7</v>
+      </c>
+      <c r="I177" s="15">
+        <v>4.7</v>
+      </c>
+      <c r="J177" s="57">
+        <v>14.3</v>
+      </c>
+      <c r="K177" s="15">
+        <v>9.6</v>
+      </c>
+      <c r="L177" s="58">
+        <v>17500</v>
+      </c>
+      <c r="M177" s="15">
+        <v>18500</v>
+      </c>
+      <c r="N177" s="59">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="O177" s="60">
+        <v>0.81700000000000006</v>
+      </c>
+      <c r="P177" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="178" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A178" t="s">
+        <v>7</v>
+      </c>
+      <c r="B178" s="52">
+        <v>29</v>
+      </c>
+      <c r="C178" s="14">
+        <v>29.5</v>
+      </c>
+      <c r="D178" s="53">
+        <v>31</v>
+      </c>
+      <c r="E178" s="54">
+        <v>3129</v>
+      </c>
+      <c r="F178" s="55">
+        <v>2.4</v>
+      </c>
+      <c r="G178">
+        <v>1</v>
+      </c>
+      <c r="H178" s="56">
+        <v>5.7</v>
+      </c>
+      <c r="I178" s="15">
+        <v>4.7</v>
+      </c>
+      <c r="J178" s="57">
+        <v>14.3</v>
+      </c>
+      <c r="K178" s="15">
+        <v>9.6</v>
+      </c>
+      <c r="L178" s="58">
+        <v>17500</v>
+      </c>
+      <c r="M178" s="15">
+        <v>18500</v>
+      </c>
+      <c r="N178" s="59">
+        <v>0.38</v>
+      </c>
+      <c r="O178" s="60">
+        <v>0.61499999999999999</v>
+      </c>
+      <c r="P178" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="179" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A179" s="61" t="s">
+        <v>4</v>
+      </c>
+      <c r="B179" s="63">
+        <v>27.75</v>
+      </c>
+      <c r="C179" s="14">
+        <v>24</v>
+      </c>
+      <c r="D179" s="64">
+        <v>1652</v>
+      </c>
+      <c r="E179" s="65">
+        <v>11745</v>
+      </c>
+      <c r="F179" s="66">
+        <v>1.9</v>
+      </c>
+      <c r="G179">
+        <v>2</v>
+      </c>
+      <c r="H179" s="67">
+        <v>6.4</v>
+      </c>
+      <c r="I179" s="15">
+        <v>6.4</v>
+      </c>
+      <c r="J179" s="68">
+        <v>13.6</v>
+      </c>
+      <c r="K179" s="15">
+        <v>13.6</v>
+      </c>
+      <c r="L179" s="69">
+        <v>18000</v>
+      </c>
+      <c r="M179" s="15">
+        <v>16500</v>
+      </c>
+      <c r="N179" s="70">
+        <v>0.66</v>
+      </c>
+      <c r="O179" s="71">
+        <v>0.996</v>
+      </c>
+      <c r="P179" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="180" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A180" s="62" t="s">
+        <v>4</v>
+      </c>
+      <c r="B180" s="63">
+        <v>27.5</v>
+      </c>
+      <c r="C180" s="14">
+        <v>24</v>
+      </c>
+      <c r="D180" s="64">
+        <v>1646</v>
+      </c>
+      <c r="E180" s="65">
+        <v>11745</v>
+      </c>
+      <c r="F180" s="66">
+        <v>1.9</v>
+      </c>
+      <c r="G180">
+        <v>2</v>
+      </c>
+      <c r="H180" s="67">
+        <v>6.4</v>
+      </c>
+      <c r="I180" s="15">
+        <v>6.4</v>
+      </c>
+      <c r="J180" s="68">
+        <v>13.6</v>
+      </c>
+      <c r="K180" s="15">
+        <v>13.6</v>
+      </c>
+      <c r="L180" s="69">
+        <v>17500</v>
+      </c>
+      <c r="M180" s="15">
+        <v>16500</v>
+      </c>
+      <c r="N180" s="70">
+        <v>0.67</v>
+      </c>
+      <c r="O180" s="71">
+        <v>0.996</v>
+      </c>
+      <c r="P180" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="181" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A181" s="62" t="s">
+        <v>4</v>
+      </c>
+      <c r="B181" s="63">
+        <v>27.25</v>
+      </c>
+      <c r="C181" s="14">
+        <v>24</v>
+      </c>
+      <c r="D181" s="64">
+        <v>1550</v>
+      </c>
+      <c r="E181" s="65">
+        <v>11745</v>
+      </c>
+      <c r="F181" s="66">
+        <v>2</v>
+      </c>
+      <c r="G181">
+        <v>2</v>
+      </c>
+      <c r="H181" s="67">
+        <v>6.4</v>
+      </c>
+      <c r="I181" s="15">
+        <v>6.4</v>
+      </c>
+      <c r="J181" s="68">
+        <v>13.6</v>
+      </c>
+      <c r="K181" s="15">
+        <v>13.6</v>
+      </c>
+      <c r="L181" s="69">
+        <v>17550</v>
+      </c>
+      <c r="M181" s="15">
+        <v>16500</v>
+      </c>
+      <c r="N181" s="70">
+        <v>0.59</v>
+      </c>
+      <c r="O181" s="71">
+        <v>0.7390000000000001</v>
+      </c>
+      <c r="P181" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="182" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A182" s="62" t="s">
+        <v>4</v>
+      </c>
+      <c r="B182" s="63">
+        <v>27.5</v>
+      </c>
+      <c r="C182" s="14">
+        <v>24</v>
+      </c>
+      <c r="D182" s="64">
+        <v>1591</v>
+      </c>
+      <c r="E182" s="65">
+        <v>11745</v>
+      </c>
+      <c r="F182" s="66">
+        <v>1.9</v>
+      </c>
+      <c r="G182">
+        <v>2</v>
+      </c>
+      <c r="H182" s="67">
+        <v>6.4</v>
+      </c>
+      <c r="I182" s="15">
+        <v>6.4</v>
+      </c>
+      <c r="J182" s="68">
+        <v>13.6</v>
+      </c>
+      <c r="K182" s="15">
+        <v>13.6</v>
+      </c>
+      <c r="L182" s="69">
+        <v>17500</v>
+      </c>
+      <c r="M182" s="15">
+        <v>16500</v>
+      </c>
+      <c r="N182" s="70">
+        <v>0.66</v>
+      </c>
+      <c r="O182" s="71">
+        <v>0.93799999999999994</v>
+      </c>
+      <c r="P182" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="183" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A183" s="62" t="s">
+        <v>4</v>
+      </c>
+      <c r="B183" s="63">
+        <v>26</v>
+      </c>
+      <c r="C183" s="14">
+        <v>24</v>
+      </c>
+      <c r="D183" s="64">
+        <v>1377</v>
+      </c>
+      <c r="E183" s="65">
+        <v>11745</v>
+      </c>
+      <c r="F183" s="66">
+        <v>1.9</v>
+      </c>
+      <c r="G183">
+        <v>2</v>
+      </c>
+      <c r="H183" s="67">
+        <v>6.8</v>
+      </c>
+      <c r="I183" s="15">
+        <v>6.4</v>
+      </c>
+      <c r="J183" s="68">
+        <v>14</v>
+      </c>
+      <c r="K183" s="15">
+        <v>13.6</v>
+      </c>
+      <c r="L183" s="69">
+        <v>17500</v>
+      </c>
+      <c r="M183" s="15">
+        <v>16500</v>
+      </c>
+      <c r="N183" s="70">
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="O183" s="71">
+        <v>0.68900000000000006</v>
+      </c>
+      <c r="P183" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="184" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A184" s="62" t="s">
+        <v>4</v>
+      </c>
+      <c r="B184" s="63">
+        <v>27</v>
+      </c>
+      <c r="C184" s="14">
+        <v>24</v>
+      </c>
+      <c r="D184" s="64">
+        <v>1463</v>
+      </c>
+      <c r="E184" s="65">
+        <v>11745</v>
+      </c>
+      <c r="F184" s="66">
+        <v>2</v>
+      </c>
+      <c r="G184">
+        <v>2</v>
+      </c>
+      <c r="H184" s="67">
+        <v>6.4</v>
+      </c>
+      <c r="I184" s="15">
+        <v>6.4</v>
+      </c>
+      <c r="J184" s="68">
+        <v>13.6</v>
+      </c>
+      <c r="K184" s="15">
+        <v>13.6</v>
+      </c>
+      <c r="L184" s="69">
+        <v>17500</v>
+      </c>
+      <c r="M184" s="15">
+        <v>16500</v>
+      </c>
+      <c r="N184" s="70">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="O184" s="71">
+        <v>0.80200000000000005</v>
+      </c>
+      <c r="P184" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="185" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A185" s="62" t="s">
+        <v>4</v>
+      </c>
+      <c r="B185" s="63">
+        <v>24.5</v>
+      </c>
+      <c r="C185" s="14">
+        <v>24</v>
+      </c>
+      <c r="D185" s="64">
+        <v>1455</v>
+      </c>
+      <c r="E185" s="65">
+        <v>11745</v>
+      </c>
+      <c r="F185" s="66">
+        <v>3.4</v>
+      </c>
+      <c r="G185">
+        <v>2</v>
+      </c>
+      <c r="H185" s="67">
+        <v>6</v>
+      </c>
+      <c r="I185" s="15">
+        <v>6.4</v>
+      </c>
+      <c r="J185" s="68">
+        <v>14.2</v>
+      </c>
+      <c r="K185" s="15">
+        <v>13.6</v>
+      </c>
+      <c r="L185" s="69">
+        <v>17000</v>
+      </c>
+      <c r="M185" s="15">
+        <v>16500</v>
+      </c>
+      <c r="N185" s="70">
+        <v>0.66</v>
+      </c>
+      <c r="O185" s="71">
+        <v>0.89800000000000002</v>
+      </c>
+      <c r="P185" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="186" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A186" s="62" t="s">
+        <v>4</v>
+      </c>
+      <c r="B186" s="63">
+        <v>28</v>
+      </c>
+      <c r="C186" s="14">
+        <v>24</v>
+      </c>
+      <c r="D186" s="64">
+        <v>998</v>
+      </c>
+      <c r="E186" s="65">
+        <v>11745</v>
+      </c>
+      <c r="F186" s="66">
+        <v>3.4</v>
+      </c>
+      <c r="G186">
+        <v>2</v>
+      </c>
+      <c r="H186" s="67">
+        <v>5.7</v>
+      </c>
+      <c r="I186" s="15">
+        <v>6.4</v>
+      </c>
+      <c r="J186" s="68">
+        <v>14.3</v>
+      </c>
+      <c r="K186" s="15">
+        <v>13.6</v>
+      </c>
+      <c r="L186" s="69">
+        <v>17500</v>
+      </c>
+      <c r="M186" s="15">
+        <v>16500</v>
+      </c>
+      <c r="N186" s="70">
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="O186" s="71">
+        <v>0.86099999999999999</v>
+      </c>
+      <c r="P186" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="187" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A187" s="62" t="s">
+        <v>4</v>
+      </c>
+      <c r="B187" s="63">
+        <v>19.25</v>
+      </c>
+      <c r="C187" s="14">
+        <v>24</v>
+      </c>
+      <c r="D187" s="64">
+        <v>5</v>
+      </c>
+      <c r="E187" s="65">
+        <v>11745</v>
+      </c>
+      <c r="F187" s="66">
+        <v>2.4</v>
+      </c>
+      <c r="G187">
+        <v>2</v>
+      </c>
+      <c r="H187" s="67">
+        <v>3.5</v>
+      </c>
+      <c r="I187" s="15">
+        <v>6.4</v>
+      </c>
+      <c r="J187" s="68">
+        <v>17.2</v>
+      </c>
+      <c r="K187" s="15">
+        <v>13.6</v>
+      </c>
+      <c r="L187" s="69">
+        <v>14000</v>
+      </c>
+      <c r="M187" s="15">
+        <v>16500</v>
+      </c>
+      <c r="N187" s="70">
+        <v>0.59</v>
+      </c>
+      <c r="O187" s="71">
+        <v>0.69499999999999995</v>
+      </c>
+      <c r="P187" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="188" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A188" s="62" t="s">
+        <v>4</v>
+      </c>
+      <c r="B188" s="63">
+        <v>33</v>
+      </c>
+      <c r="C188" s="14">
+        <v>24</v>
+      </c>
+      <c r="D188" s="64">
+        <v>4</v>
+      </c>
+      <c r="E188" s="65">
+        <v>11745</v>
+      </c>
+      <c r="F188" s="66">
+        <v>4.5</v>
+      </c>
+      <c r="G188">
+        <v>2</v>
+      </c>
+      <c r="H188" s="67">
+        <v>9.4</v>
+      </c>
+      <c r="I188" s="15">
+        <v>6.4</v>
+      </c>
+      <c r="J188" s="68">
+        <v>15.5</v>
+      </c>
+      <c r="K188" s="15">
+        <v>13.6</v>
+      </c>
+      <c r="L188" s="69">
+        <v>25000</v>
+      </c>
+      <c r="M188" s="15">
+        <v>16500</v>
+      </c>
+      <c r="N188" s="70">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="O188" s="71">
+        <v>0.40500000000000003</v>
+      </c>
+      <c r="P188" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="189" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A189" s="62" t="s">
+        <v>4</v>
+      </c>
+      <c r="B189" s="63">
+        <v>19</v>
+      </c>
+      <c r="C189" s="14">
+        <v>24</v>
+      </c>
+      <c r="D189" s="64">
+        <v>2</v>
+      </c>
+      <c r="E189" s="65">
+        <v>11745</v>
+      </c>
+      <c r="F189" s="66">
+        <v>3.6</v>
+      </c>
+      <c r="G189">
+        <v>2</v>
+      </c>
+      <c r="H189" s="67">
+        <v>2.7</v>
+      </c>
+      <c r="I189" s="15">
+        <v>6.4</v>
+      </c>
+      <c r="J189" s="68">
+        <v>17.3</v>
+      </c>
+      <c r="K189" s="15">
+        <v>13.6</v>
+      </c>
+      <c r="L189" s="69">
+        <v>14000</v>
+      </c>
+      <c r="M189" s="15">
+        <v>16500</v>
+      </c>
+      <c r="N189" s="70">
+        <v>0.66</v>
+      </c>
+      <c r="O189" s="71">
+        <v>0.89300000000000002</v>
+      </c>
+      <c r="P189" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="190" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A190" s="62" t="s">
+        <v>4</v>
+      </c>
+      <c r="B190" s="63">
+        <v>19</v>
+      </c>
+      <c r="C190" s="14">
+        <v>24</v>
+      </c>
+      <c r="D190" s="64">
+        <v>2</v>
+      </c>
+      <c r="E190" s="65">
+        <v>11745</v>
+      </c>
+      <c r="F190" s="66">
+        <v>6.6</v>
+      </c>
+      <c r="G190">
+        <v>2</v>
+      </c>
+      <c r="H190" s="67">
+        <v>3</v>
+      </c>
+      <c r="I190" s="15">
+        <v>6.4</v>
+      </c>
+      <c r="J190" s="68">
+        <v>17</v>
+      </c>
+      <c r="K190" s="15">
+        <v>13.6</v>
+      </c>
+      <c r="L190" s="69">
+        <v>14000</v>
+      </c>
+      <c r="M190" s="15">
+        <v>16500</v>
+      </c>
+      <c r="N190" s="70">
+        <v>0.67</v>
+      </c>
+      <c r="O190" s="71">
+        <v>0.98199999999999998</v>
+      </c>
+      <c r="P190" t="s">
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -9645,9 +13434,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5359C924-766F-41BE-9B45-0D62BFF47031}">
   <dimension ref="A1:I118"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
         <v>25</v>
       </c>
@@ -9676,7 +13465,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>0.21362689675691759</v>
       </c>
@@ -9705,7 +13494,7 @@
         <v>0.64599999999999991</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>0.20187444213031835</v>
       </c>
@@ -9734,7 +13523,7 @@
         <v>0.81700000000000006</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>0.1902707527521571</v>
       </c>
@@ -9763,7 +13552,7 @@
         <v>0.58299999999999996</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>0.17003867896459388</v>
       </c>
@@ -9792,7 +13581,7 @@
         <v>0.58299999999999996</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>0.14861648318952692</v>
       </c>
@@ -9821,7 +13610,7 @@
         <v>0.58299999999999996</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>0.15610786224821313</v>
       </c>
@@ -9850,7 +13639,7 @@
         <v>0.55000000000000004</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>0.23594293250209808</v>
       </c>
@@ -9879,7 +13668,7 @@
         <v>0.624</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>0.29588778323941972</v>
       </c>
@@ -9908,7 +13697,7 @@
         <v>0.52900000000000003</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>0.17587819206330177</v>
       </c>
@@ -9937,7 +13726,7 @@
         <v>0.79599999999999993</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>0.1563361707229349</v>
       </c>
@@ -9966,7 +13755,7 @@
         <v>0.52900000000000003</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>0.13535547296487233</v>
       </c>
@@ -9995,7 +13784,7 @@
         <v>0.52900000000000003</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>0.19994643096290343</v>
       </c>
@@ -10024,7 +13813,7 @@
         <v>0.51700000000000002</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>0.25798625151637689</v>
       </c>
@@ -10053,7 +13842,7 @@
         <v>0.77400000000000002</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>0.17185604528912252</v>
       </c>
@@ -10082,7 +13871,7 @@
         <v>0.60299999999999998</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>0.16942984229680549</v>
       </c>
@@ -10111,7 +13900,7 @@
         <v>0.47600000000000003</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>0.1678123736352608</v>
       </c>
@@ -10140,7 +13929,7 @@
         <v>0.47600000000000003</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>0.13465426607359482</v>
       </c>
@@ -10169,7 +13958,7 @@
         <v>0.47600000000000003</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>0.17199248120300753</v>
       </c>
@@ -10198,7 +13987,7 @@
         <v>0.48599999999999999</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>0.2536610878661088</v>
       </c>
@@ -10227,7 +14016,7 @@
         <v>0.754</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>0.23012552301255229</v>
       </c>
@@ -10256,7 +14045,7 @@
         <v>0.58200000000000007</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>0.18828451882845187</v>
       </c>
@@ -10285,7 +14074,7 @@
         <v>0.42499999999999999</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>0.16370292887029289</v>
       </c>
@@ -10314,7 +14103,7 @@
         <v>0.42499999999999999</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>0.15847280334728034</v>
       </c>
@@ -10343,7 +14132,7 @@
         <v>0.42499999999999999</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>0.19862155388471178</v>
       </c>
@@ -10372,7 +14161,7 @@
         <v>0.45500000000000002</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>0.2608695652173913</v>
       </c>
@@ -10401,7 +14190,7 @@
         <v>0.754</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>0.23785166240409208</v>
       </c>
@@ -10430,7 +14219,7 @@
         <v>0.42499999999999999</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>0.15907928388746803</v>
       </c>
@@ -10459,7 +14248,7 @@
         <v>0.503</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>0.14373401534526853</v>
       </c>
@@ -10488,7 +14277,7 @@
         <v>0.42499999999999999</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>0.13606138107416879</v>
       </c>
@@ -10517,7 +14306,7 @@
         <v>0.42499999999999999</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>0.18572292800967938</v>
       </c>
@@ -10546,7 +14335,7 @@
         <v>0.45500000000000002</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>0.21020529604284438</v>
       </c>
@@ -10575,7 +14364,7 @@
         <v>0.67500000000000004</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>0.19428741445998216</v>
       </c>
@@ -10604,7 +14393,7 @@
         <v>0.55100000000000005</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>0.24799166914608747</v>
       </c>
@@ -10633,7 +14422,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>0.19696518893186551</v>
       </c>
@@ -10662,7 +14451,7 @@
         <v>0.81700000000000006</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>8.0779529901814931E-2</v>
       </c>
@@ -10691,7 +14480,7 @@
         <v>0.58299999999999996</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>2.1719726271942873E-2</v>
       </c>
@@ -10720,7 +14509,7 @@
         <v>0.79599999999999993</v>
       </c>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>1.3240107110978875E-2</v>
       </c>
@@ -10749,7 +14538,7 @@
         <v>0.52900000000000003</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>1.3240107110978875E-2</v>
       </c>
@@ -10778,7 +14567,7 @@
         <v>0.624</v>
       </c>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>1.5620351085986313E-2</v>
       </c>
@@ -10807,7 +14596,7 @@
         <v>0.70599999999999996</v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>4.0166617078250524E-3</v>
       </c>
@@ -10836,7 +14625,7 @@
         <v>0.52900000000000003</v>
       </c>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>7.4382624218982446E-4</v>
       </c>
@@ -10865,7 +14654,7 @@
         <v>0.42499999999999999</v>
       </c>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>8.9259149062778935E-4</v>
       </c>
@@ -10894,7 +14683,7 @@
         <v>0.754</v>
       </c>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>0.23462414578587698</v>
       </c>
@@ -10923,7 +14712,7 @@
         <v>0.52900000000000003</v>
       </c>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>0.22215561683251409</v>
       </c>
@@ -10952,7 +14741,7 @@
         <v>0.624</v>
       </c>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>0.2280302122047716</v>
       </c>
@@ -10981,7 +14770,7 @@
         <v>0.79599999999999993</v>
       </c>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>0.13235823042800623</v>
       </c>
@@ -11010,7 +14799,7 @@
         <v>0.52900000000000003</v>
       </c>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>0.18091355952523677</v>
       </c>
@@ -11039,7 +14828,7 @@
         <v>0.70599999999999996</v>
       </c>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>1.1988970147464332E-3</v>
       </c>
@@ -11068,7 +14857,7 @@
         <v>0.58299999999999996</v>
       </c>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>2.3977940294928664E-4</v>
       </c>
@@ -11097,7 +14886,7 @@
         <v>0.55100000000000005</v>
       </c>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>1.1988970147464332E-4</v>
       </c>
@@ -11126,7 +14915,7 @@
         <v>0.81700000000000006</v>
       </c>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>0.21876263647391833</v>
       </c>
@@ -11155,7 +14944,7 @@
         <v>0.77400000000000002</v>
       </c>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>0.2329154872624343</v>
       </c>
@@ -11184,7 +14973,7 @@
         <v>0.63200000000000001</v>
       </c>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>0.18924383340072787</v>
       </c>
@@ -11213,7 +15002,7 @@
         <v>0.65900000000000003</v>
       </c>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>0.15082895268904165</v>
       </c>
@@ -11242,7 +15031,7 @@
         <v>0.60299999999999998</v>
       </c>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>0.12656692276587142</v>
       </c>
@@ -11271,7 +15060,7 @@
         <v>0.47600000000000003</v>
       </c>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>1.6174686615446826E-2</v>
       </c>
@@ -11300,7 +15089,7 @@
         <v>0.754</v>
       </c>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A58">
         <v>1.1322280630812778E-2</v>
       </c>
@@ -11329,7 +15118,7 @@
         <v>0.77800000000000002</v>
       </c>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A59">
         <v>8.8960776384957533E-3</v>
       </c>
@@ -11358,7 +15147,7 @@
         <v>0.42499999999999999</v>
       </c>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A60">
         <v>8.491710473109584E-3</v>
       </c>
@@ -11387,7 +15176,7 @@
         <v>0.58200000000000007</v>
       </c>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A61">
         <v>8.491710473109584E-3</v>
       </c>
@@ -11416,7 +15205,7 @@
         <v>0.81700000000000006</v>
       </c>
     </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A62">
         <v>8.087343307723413E-3</v>
       </c>
@@ -11445,7 +15234,7 @@
         <v>0.55100000000000005</v>
       </c>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A63">
         <v>5.6611403154063888E-3</v>
       </c>
@@ -11474,7 +15263,7 @@
         <v>0.55100000000000005</v>
       </c>
     </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A64">
         <v>0.27039748953974896</v>
       </c>
@@ -11503,7 +15292,7 @@
         <v>0.77800000000000002</v>
       </c>
     </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A65">
         <v>0.22228033472803346</v>
       </c>
@@ -11532,7 +15321,7 @@
         <v>0.754</v>
       </c>
     </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A66">
         <v>0.19874476987447698</v>
       </c>
@@ -11561,7 +15350,7 @@
         <v>0.58200000000000007</v>
       </c>
     </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A67">
         <v>0.17311715481171547</v>
       </c>
@@ -11590,7 +15379,7 @@
         <v>0.55100000000000005</v>
       </c>
     </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A68">
         <v>0.13179916317991633</v>
       </c>
@@ -11619,7 +15408,7 @@
         <v>0.42499999999999999</v>
       </c>
     </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A69">
         <v>1.5690376569037657E-3</v>
       </c>
@@ -11648,7 +15437,7 @@
         <v>0.55100000000000005</v>
       </c>
     </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A70">
         <v>5.2301255230125519E-4</v>
       </c>
@@ -11677,7 +15466,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A71">
         <v>1.0460251046025104E-3</v>
       </c>
@@ -11706,7 +15495,7 @@
         <v>0.81700000000000006</v>
       </c>
     </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A72">
         <v>0.2</v>
       </c>
@@ -11735,7 +15524,7 @@
         <v>0.754</v>
       </c>
     </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A73">
         <v>0.34731457800511512</v>
       </c>
@@ -11764,7 +15553,7 @@
         <v>0.754</v>
       </c>
     </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A74">
         <v>0.25677749360613811</v>
       </c>
@@ -11793,7 +15582,7 @@
         <v>0.55100000000000005</v>
       </c>
     </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A75">
         <v>0.11815856777493607</v>
       </c>
@@ -11822,7 +15611,7 @@
         <v>0.42499999999999999</v>
       </c>
     </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A76">
         <v>1.9437340153452685E-2</v>
       </c>
@@ -11851,7 +15640,7 @@
         <v>0.55100000000000005</v>
       </c>
     </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A77">
         <v>1.7391304347826087E-2</v>
       </c>
@@ -11880,7 +15669,7 @@
         <v>0.81700000000000006</v>
       </c>
     </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A78">
         <v>2.4552429667519183E-2</v>
       </c>
@@ -11909,7 +15698,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A79">
         <v>1.1764705882352941E-2</v>
       </c>
@@ -11938,7 +15727,7 @@
         <v>0.67500000000000004</v>
       </c>
     </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A80">
         <v>5.6265984654731462E-3</v>
       </c>
@@ -11967,7 +15756,7 @@
         <v>0.58299999999999996</v>
       </c>
     </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A81">
         <v>0.240566680288789</v>
       </c>
@@ -11996,7 +15785,7 @@
         <v>0.88500000000000001</v>
       </c>
     </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A82">
         <v>0.21577441765427052</v>
       </c>
@@ -12025,7 +15814,7 @@
         <v>0.75900000000000001</v>
       </c>
     </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A83">
         <v>0.24751396267538484</v>
       </c>
@@ -12054,7 +15843,7 @@
         <v>0.996</v>
       </c>
     </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A84">
         <v>0.19956409208554693</v>
       </c>
@@ -12083,7 +15872,7 @@
         <v>0.70299999999999996</v>
       </c>
     </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A85">
         <v>9.6172183626208968E-2</v>
       </c>
@@ -12112,7 +15901,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="86" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A86">
         <v>2.7244244653316989E-4</v>
       </c>
@@ -12141,7 +15930,7 @@
         <v>0.98199999999999998</v>
       </c>
     </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A87">
         <v>0.20867325032202663</v>
       </c>
@@ -12170,7 +15959,7 @@
         <v>0.752</v>
       </c>
     </row>
-    <row r="88" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A88">
         <v>0.2182267067410906</v>
       </c>
@@ -12199,7 +15988,7 @@
         <v>0.98199999999999998</v>
       </c>
     </row>
-    <row r="89" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A89">
         <v>0.19353799914126235</v>
       </c>
@@ -12228,7 +16017,7 @@
         <v>0.68900000000000006</v>
       </c>
     </row>
-    <row r="90" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A90">
         <v>0.20513095749248605</v>
       </c>
@@ -12257,7 +16046,7 @@
         <v>0.83200000000000007</v>
       </c>
     </row>
-    <row r="91" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A91">
         <v>0.16981537140403608</v>
       </c>
@@ -12286,7 +16075,7 @@
         <v>0.71400000000000008</v>
       </c>
     </row>
-    <row r="92" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A92">
         <v>1.3954486904250751E-3</v>
       </c>
@@ -12315,7 +16104,7 @@
         <v>0.70299999999999996</v>
       </c>
     </row>
-    <row r="93" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A93">
         <v>1.2881064834693002E-3</v>
       </c>
@@ -12344,7 +16133,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="94" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A94">
         <v>1.0734220695577501E-3</v>
       </c>
@@ -12373,7 +16162,7 @@
         <v>0.88500000000000001</v>
       </c>
     </row>
-    <row r="95" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A95">
         <v>1.0734220695577501E-3</v>
       </c>
@@ -12402,7 +16191,7 @@
         <v>0.75900000000000001</v>
       </c>
     </row>
-    <row r="96" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A96">
         <v>0.17890706578489385</v>
       </c>
@@ -12431,7 +16220,7 @@
         <v>0.878</v>
       </c>
     </row>
-    <row r="97" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A97">
         <v>0.16463626870866691</v>
       </c>
@@ -12460,7 +16249,7 @@
         <v>0.80599999999999994</v>
       </c>
     </row>
-    <row r="98" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A98">
         <v>0.25965889314305601</v>
       </c>
@@ -12489,7 +16278,7 @@
         <v>0.96799999999999997</v>
       </c>
     </row>
-    <row r="99" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A99">
         <v>0.27323355377654018</v>
       </c>
@@ -12518,7 +16307,7 @@
         <v>0.68099999999999994</v>
       </c>
     </row>
-    <row r="100" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A100">
         <v>0.11451444483118692</v>
       </c>
@@ -12547,7 +16336,7 @@
         <v>0.76800000000000002</v>
       </c>
     </row>
-    <row r="101" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A101">
         <v>4.1768186564566656E-3</v>
       </c>
@@ -12576,7 +16365,7 @@
         <v>0.64400000000000002</v>
       </c>
     </row>
-    <row r="102" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A102">
         <v>3.4806822137138879E-3</v>
       </c>
@@ -12605,7 +16394,7 @@
         <v>0.996</v>
       </c>
     </row>
-    <row r="103" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A103">
         <v>6.9613644274277764E-4</v>
       </c>
@@ -12634,7 +16423,7 @@
         <v>0.88500000000000001</v>
       </c>
     </row>
-    <row r="104" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A104">
         <v>6.9613644274277764E-4</v>
       </c>
@@ -12663,7 +16452,7 @@
         <v>0.75900000000000001</v>
       </c>
     </row>
-    <row r="105" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A105">
         <v>0.32998690528153646</v>
       </c>
@@ -12692,7 +16481,7 @@
         <v>0.85499999999999998</v>
       </c>
     </row>
-    <row r="106" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A106">
         <v>0.24312527280663465</v>
       </c>
@@ -12721,7 +16510,7 @@
         <v>0.74900000000000011</v>
       </c>
     </row>
-    <row r="107" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A107">
         <v>0.18900043649061546</v>
       </c>
@@ -12750,7 +16539,7 @@
         <v>0.95400000000000007</v>
       </c>
     </row>
-    <row r="108" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A108">
         <v>0.17546922741161064</v>
       </c>
@@ -12779,7 +16568,7 @@
         <v>0.61599999999999999</v>
       </c>
     </row>
-    <row r="109" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A109">
         <v>6.1981667394151028E-2</v>
       </c>
@@ -12808,7 +16597,7 @@
         <v>0.64400000000000002</v>
       </c>
     </row>
-    <row r="110" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A110">
         <v>0.22611327280587981</v>
       </c>
@@ -12837,7 +16626,7 @@
         <v>0.95400000000000007</v>
       </c>
     </row>
-    <row r="111" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A111">
         <v>0.23000432338953739</v>
       </c>
@@ -12866,7 +16655,7 @@
         <v>0.61599999999999999</v>
       </c>
     </row>
-    <row r="112" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A112">
         <v>0.41374837872892345</v>
       </c>
@@ -12895,7 +16684,7 @@
         <v>0.95400000000000007</v>
       </c>
     </row>
-    <row r="113" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A113">
         <v>6.9174232598357116E-2</v>
       </c>
@@ -12924,7 +16713,7 @@
         <v>0.64400000000000002</v>
       </c>
     </row>
-    <row r="114" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A114">
         <v>2.1184608733246867E-2</v>
       </c>
@@ -12953,7 +16742,7 @@
         <v>0.70299999999999996</v>
       </c>
     </row>
-    <row r="115" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A115">
         <v>3.372243839169909E-2</v>
       </c>
@@ -12982,7 +16771,7 @@
         <v>0.996</v>
       </c>
     </row>
-    <row r="116" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A116">
         <v>4.755728491137051E-3</v>
       </c>
@@ -13011,7 +16800,7 @@
         <v>0.88500000000000001</v>
       </c>
     </row>
-    <row r="117" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A117">
         <v>1.2970168612191958E-3</v>
       </c>
@@ -13040,7 +16829,7 @@
         <v>0.75900000000000001</v>
       </c>
     </row>
-    <row r="118" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A118">
         <v>8.6467790747946386E-4</v>
       </c>
